--- a/artfynd/A 38064-2024 artfynd.xlsx
+++ b/artfynd/A 38064-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120315903</v>
+        <v>120315897</v>
       </c>
       <c r="B2" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -708,12 +708,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -723,10 +731,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>376869</v>
+        <v>376875</v>
       </c>
       <c r="R2" t="n">
-        <v>6928711</v>
+        <v>6928715</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,6 +767,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Observerad under flera tillfällen under besöket</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,10 +798,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120315914</v>
+        <v>120315938</v>
       </c>
       <c r="B3" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -833,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>376706</v>
+        <v>376753</v>
       </c>
       <c r="R3" t="n">
-        <v>6928747</v>
+        <v>6928863</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120315897</v>
+        <v>120315911</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,39 +924,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>376875</v>
+        <v>376797</v>
       </c>
       <c r="R4" t="n">
-        <v>6928715</v>
+        <v>6928695</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,7 +991,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Observerad under flera tillfällen under besöket</t>
+          <t>Flera platser i området</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,6 +1000,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1018,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120315910</v>
+        <v>120315914</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>376797</v>
+        <v>376706</v>
       </c>
       <c r="R5" t="n">
-        <v>6928695</v>
+        <v>6928747</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120315938</v>
+        <v>120315928</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>78278</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,31 +1145,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1176,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>376753</v>
+        <v>376678</v>
       </c>
       <c r="R6" t="n">
-        <v>6928863</v>
+        <v>6928776</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,12 +1210,18 @@
           <t>2024-10-09</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Flera platser i området</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1238,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120315928</v>
+        <v>120315903</v>
       </c>
       <c r="B7" t="n">
-        <v>78262</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,26 +1256,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1281,10 +1288,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>376678</v>
+        <v>376869</v>
       </c>
       <c r="R7" t="n">
-        <v>6928776</v>
+        <v>6928711</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,18 +1326,12 @@
           <t>2024-10-09</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Flera platser i området</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1349,10 +1350,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120315911</v>
+        <v>120315910</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1365,26 +1366,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1430,18 +1436,12 @@
           <t>2024-10-09</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Flera platser i området</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 38064-2024 artfynd.xlsx
+++ b/artfynd/A 38064-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120315897</v>
+        <v>120315903</v>
       </c>
       <c r="B2" t="n">
         <v>57320</v>
@@ -708,20 +708,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -731,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>376875</v>
+        <v>376869</v>
       </c>
       <c r="R2" t="n">
-        <v>6928715</v>
+        <v>6928711</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -767,11 +759,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-09</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Observerad under flera tillfällen under besöket</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120315938</v>
+        <v>120315910</v>
       </c>
       <c r="B3" t="n">
         <v>57320</v>
@@ -846,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>376753</v>
+        <v>376797</v>
       </c>
       <c r="R3" t="n">
-        <v>6928863</v>
+        <v>6928695</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -908,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120315911</v>
+        <v>120315914</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,26 +911,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -951,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>376797</v>
+        <v>376706</v>
       </c>
       <c r="R4" t="n">
-        <v>6928695</v>
+        <v>6928747</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,18 +981,12 @@
           <t>2024-10-09</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Flera platser i området</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1019,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120315914</v>
+        <v>120315928</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>78278</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,31 +1021,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1067,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>376706</v>
+        <v>376678</v>
       </c>
       <c r="R5" t="n">
-        <v>6928747</v>
+        <v>6928776</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,12 +1086,18 @@
           <t>2024-10-09</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Flera platser i området</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1129,10 +1116,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120315928</v>
+        <v>120315897</v>
       </c>
       <c r="B6" t="n">
-        <v>78278</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,26 +1132,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1172,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>376678</v>
+        <v>376875</v>
       </c>
       <c r="R6" t="n">
-        <v>6928776</v>
+        <v>6928715</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Flera platser i området</t>
+          <t>Observerad under flera tillfällen under besöket</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1221,7 +1221,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1240,7 +1239,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120315903</v>
+        <v>120315938</v>
       </c>
       <c r="B7" t="n">
         <v>57320</v>
@@ -1288,10 +1287,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>376869</v>
+        <v>376753</v>
       </c>
       <c r="R7" t="n">
-        <v>6928711</v>
+        <v>6928863</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1350,10 +1349,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120315910</v>
+        <v>120315911</v>
       </c>
       <c r="B8" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1366,31 +1365,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1436,12 +1430,18 @@
           <t>2024-10-09</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Flera platser i området</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 38064-2024 artfynd.xlsx
+++ b/artfynd/A 38064-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120315903</v>
+        <v>120315911</v>
       </c>
       <c r="B2" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>376869</v>
+        <v>376797</v>
       </c>
       <c r="R2" t="n">
-        <v>6928711</v>
+        <v>6928695</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,12 +756,18 @@
           <t>2024-10-09</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Flera platser i området</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -895,7 +896,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120315914</v>
+        <v>120315903</v>
       </c>
       <c r="B4" t="n">
         <v>57320</v>
@@ -943,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>376706</v>
+        <v>376869</v>
       </c>
       <c r="R4" t="n">
-        <v>6928747</v>
+        <v>6928711</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120315928</v>
+        <v>120315897</v>
       </c>
       <c r="B5" t="n">
-        <v>78278</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,26 +1022,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1048,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>376678</v>
+        <v>376875</v>
       </c>
       <c r="R5" t="n">
-        <v>6928776</v>
+        <v>6928715</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1102,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Flera platser i området</t>
+          <t>Observerad under flera tillfällen under besöket</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,7 +1111,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1116,7 +1129,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120315897</v>
+        <v>120315938</v>
       </c>
       <c r="B6" t="n">
         <v>57320</v>
@@ -1149,20 +1162,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1172,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>376875</v>
+        <v>376753</v>
       </c>
       <c r="R6" t="n">
-        <v>6928715</v>
+        <v>6928863</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,11 +1213,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-09</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Observerad under flera tillfällen under besöket</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120315938</v>
+        <v>120315928</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>78278</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1255,31 +1255,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1287,10 +1282,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>376753</v>
+        <v>376678</v>
       </c>
       <c r="R7" t="n">
-        <v>6928863</v>
+        <v>6928776</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,12 +1320,18 @@
           <t>2024-10-09</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Flera platser i området</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1349,10 +1350,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120315911</v>
+        <v>120315914</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1365,26 +1366,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1392,10 +1398,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>376797</v>
+        <v>376706</v>
       </c>
       <c r="R8" t="n">
-        <v>6928695</v>
+        <v>6928747</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1430,18 +1436,12 @@
           <t>2024-10-09</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Flera platser i området</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 38064-2024 artfynd.xlsx
+++ b/artfynd/A 38064-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1458,6 +1458,6753 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120461553</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79624</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>376797</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6928714</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120464397</v>
+      </c>
+      <c r="B10" t="n">
+        <v>56532</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>övernattning</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>376843</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6928942</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120464383</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>376836</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6928949</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120464218</v>
+      </c>
+      <c r="B12" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>376778</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6928905</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120464351</v>
+      </c>
+      <c r="B13" t="n">
+        <v>74654</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>376822</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6928965</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120461902</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>376797</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6928746</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120461491</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>376797</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6928714</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120463172</v>
+      </c>
+      <c r="B16" t="n">
+        <v>90864</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>658</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Rödtjärnbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>376427</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6928969</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120462738</v>
+      </c>
+      <c r="B17" t="n">
+        <v>90594</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>376546</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6928799</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120463824</v>
+      </c>
+      <c r="B18" t="n">
+        <v>74654</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>376695</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6928830</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120464475</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>376903</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6928887</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120464038</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>376719</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6928860</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120463769</v>
+      </c>
+      <c r="B21" t="n">
+        <v>74654</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Rödtjärnbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>376666</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6928860</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120463188</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Rödtjärnbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>376452</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6928954</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120462796</v>
+      </c>
+      <c r="B23" t="n">
+        <v>74654</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>376500</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6928798</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120462344</v>
+      </c>
+      <c r="B24" t="n">
+        <v>90598</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>376677</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6928749</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120461918</v>
+      </c>
+      <c r="B25" t="n">
+        <v>74654</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>376774</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6928741</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120462917</v>
+      </c>
+      <c r="B26" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>376403</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6928904</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120462799</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78543</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>376432</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6928842</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120464205</v>
+      </c>
+      <c r="B28" t="n">
+        <v>90598</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>376778</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6928905</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>120464355</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>376822</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6928965</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>120463458</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79624</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Rödtjärnbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>376530</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6928871</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>120463009</v>
+      </c>
+      <c r="B31" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>376424</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6928913</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>120464111</v>
+      </c>
+      <c r="B32" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>376700</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6928867</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>120462971</v>
+      </c>
+      <c r="B33" t="n">
+        <v>78543</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>376410</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6928948</v>
+      </c>
+      <c r="S33" t="n">
+        <v>4</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>120462219</v>
+      </c>
+      <c r="B34" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>376700</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6928752</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>120463773</v>
+      </c>
+      <c r="B35" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Rödtjärnbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>376666</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6928860</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>120461364</v>
+      </c>
+      <c r="B36" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>376857</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6928677</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>120462766</v>
+      </c>
+      <c r="B37" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>376533</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6928800</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>120463512</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78543</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>376585</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6928865</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>120464110</v>
+      </c>
+      <c r="B39" t="n">
+        <v>90598</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>376748</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6928890</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>120461419</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79624</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>376841</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6928719</v>
+      </c>
+      <c r="S40" t="n">
+        <v>4</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>120462634</v>
+      </c>
+      <c r="B41" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>376605</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6928771</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>120462911</v>
+      </c>
+      <c r="B42" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Rödtjärnbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>376433</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6928842</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>120462884</v>
+      </c>
+      <c r="B43" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>376415</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6928886</v>
+      </c>
+      <c r="S43" t="n">
+        <v>4</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>120463679</v>
+      </c>
+      <c r="B44" t="n">
+        <v>90598</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>376629</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6928862</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>120462931</v>
+      </c>
+      <c r="B45" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>376436</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6928867</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>120463133</v>
+      </c>
+      <c r="B46" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>376426</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6928956</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>120463433</v>
+      </c>
+      <c r="B47" t="n">
+        <v>78543</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>376511</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6928908</v>
+      </c>
+      <c r="S47" t="n">
+        <v>3</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>120462877</v>
+      </c>
+      <c r="B48" t="n">
+        <v>74654</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Rödtjärnbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>376442</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6928809</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>120464178</v>
+      </c>
+      <c r="B49" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>376767</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6928875</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>120462773</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79624</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>376533</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6928800</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>120463089</v>
+      </c>
+      <c r="B51" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>376419</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6928951</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>120461440</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79659</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>376797</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6928714</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>120461382</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79624</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>376842</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6928689</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>120463175</v>
+      </c>
+      <c r="B54" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Rödtjärnbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>376427</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6928969</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>120462872</v>
+      </c>
+      <c r="B55" t="n">
+        <v>78543</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>376420</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6928868</v>
+      </c>
+      <c r="S55" t="n">
+        <v>3</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>120462709</v>
+      </c>
+      <c r="B56" t="n">
+        <v>90598</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>376574</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6928783</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>120462573</v>
+      </c>
+      <c r="B57" t="n">
+        <v>74654</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>376605</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6928771</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>120463131</v>
+      </c>
+      <c r="B58" t="n">
+        <v>78543</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>376470</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6928960</v>
+      </c>
+      <c r="S58" t="n">
+        <v>4</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>120464210</v>
+      </c>
+      <c r="B59" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>376763</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6928949</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>120464085</v>
+      </c>
+      <c r="B60" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>376731</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6928890</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>120463161</v>
+      </c>
+      <c r="B61" t="n">
+        <v>78543</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>376500</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6928936</v>
+      </c>
+      <c r="S61" t="n">
+        <v>3</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>120463199</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79624</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Rödtjärnbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>376466</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6928935</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>120462783</v>
+      </c>
+      <c r="B63" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>376448</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6928821</v>
+      </c>
+      <c r="S63" t="n">
+        <v>3</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>120461973</v>
+      </c>
+      <c r="B64" t="n">
+        <v>74654</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>376741</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6928740</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>120462372</v>
+      </c>
+      <c r="B65" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>376659</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6928762</v>
+      </c>
+      <c r="S65" t="n">
+        <v>4</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>120461377</v>
+      </c>
+      <c r="B66" t="n">
+        <v>79624</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>376858</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6928712</v>
+      </c>
+      <c r="S66" t="n">
+        <v>4</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>120461861</v>
+      </c>
+      <c r="B67" t="n">
+        <v>74654</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>376772</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6928732</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>120461976</v>
+      </c>
+      <c r="B68" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>376741</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6928740</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>120464020</v>
+      </c>
+      <c r="B69" t="n">
+        <v>79624</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>376688</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6928842</v>
+      </c>
+      <c r="S69" t="n">
+        <v>4</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>120463650</v>
+      </c>
+      <c r="B70" t="n">
+        <v>78641</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>967</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Varglav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Letharia vulpina</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) Hue</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Rödtjärnbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>376627</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6928864</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>120464264</v>
+      </c>
+      <c r="B71" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>376784</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6928921</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>120463768</v>
+      </c>
+      <c r="B72" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>376653</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6928851</v>
+      </c>
+      <c r="S72" t="n">
+        <v>4</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>120463914</v>
+      </c>
+      <c r="B73" t="n">
+        <v>90576</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Rödtjärnbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>376684</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6928823</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>120461838</v>
+      </c>
+      <c r="B74" t="n">
+        <v>79624</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>376813</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6928747</v>
+      </c>
+      <c r="S74" t="n">
+        <v>3</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38064-2024 artfynd.xlsx
+++ b/artfynd/A 38064-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120315911</v>
+        <v>120315938</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>376797</v>
+        <v>376753</v>
       </c>
       <c r="R2" t="n">
-        <v>6928695</v>
+        <v>6928863</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,18 +761,12 @@
           <t>2024-10-09</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Flera platser i området</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -896,7 +895,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120315903</v>
+        <v>120315897</v>
       </c>
       <c r="B4" t="n">
         <v>57320</v>
@@ -929,12 +928,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -944,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>376869</v>
+        <v>376875</v>
       </c>
       <c r="R4" t="n">
-        <v>6928711</v>
+        <v>6928715</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,6 +987,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Observerad under flera tillfällen under besöket</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120315897</v>
+        <v>120315911</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,39 +1034,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1062,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>376875</v>
+        <v>376797</v>
       </c>
       <c r="R5" t="n">
-        <v>6928715</v>
+        <v>6928695</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,7 +1101,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Observerad under flera tillfällen under besöket</t>
+          <t>Flera platser i området</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,6 +1110,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1129,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120315938</v>
+        <v>120315928</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>78278</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,31 +1145,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1177,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>376753</v>
+        <v>376678</v>
       </c>
       <c r="R6" t="n">
-        <v>6928863</v>
+        <v>6928776</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,12 +1210,18 @@
           <t>2024-10-09</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Flera platser i området</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1239,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120315928</v>
+        <v>120315903</v>
       </c>
       <c r="B7" t="n">
-        <v>78278</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1255,26 +1256,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1282,10 +1288,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>376678</v>
+        <v>376869</v>
       </c>
       <c r="R7" t="n">
-        <v>6928776</v>
+        <v>6928711</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,18 +1326,12 @@
           <t>2024-10-09</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Flera platser i området</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120461553</v>
+        <v>120462911</v>
       </c>
       <c r="B9" t="n">
-        <v>79624</v>
+        <v>90580</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1476,34 +1476,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>376797</v>
+        <v>376433</v>
       </c>
       <c r="R9" t="n">
-        <v>6928714</v>
+        <v>6928842</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,10 +1562,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120464397</v>
+        <v>120462796</v>
       </c>
       <c r="B10" t="n">
-        <v>56532</v>
+        <v>74654</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1574,56 +1574,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>övernattning</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>376843</v>
+        <v>376500</v>
       </c>
       <c r="R10" t="n">
-        <v>6928942</v>
+        <v>6928798</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1679,10 +1664,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120464383</v>
+        <v>120463824</v>
       </c>
       <c r="B11" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1695,37 +1680,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>376836</v>
+        <v>376695</v>
       </c>
       <c r="R11" t="n">
-        <v>6928949</v>
+        <v>6928830</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1769,22 +1754,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120464218</v>
+        <v>120463458</v>
       </c>
       <c r="B12" t="n">
-        <v>90580</v>
+        <v>79624</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1797,34 +1782,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>376778</v>
+        <v>376530</v>
       </c>
       <c r="R12" t="n">
-        <v>6928905</v>
+        <v>6928871</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1883,10 +1868,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120464351</v>
+        <v>120464038</v>
       </c>
       <c r="B13" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1899,21 +1884,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1923,10 +1908,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>376822</v>
+        <v>376719</v>
       </c>
       <c r="R13" t="n">
-        <v>6928965</v>
+        <v>6928860</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1985,7 +1970,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120461902</v>
+        <v>120462917</v>
       </c>
       <c r="B14" t="n">
         <v>78542</v>
@@ -2021,17 +2006,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>376797</v>
+        <v>376403</v>
       </c>
       <c r="R14" t="n">
-        <v>6928746</v>
+        <v>6928904</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2087,10 +2072,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120461491</v>
+        <v>120462799</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>78543</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2103,16 +2088,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2127,13 +2112,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>376797</v>
+        <v>376432</v>
       </c>
       <c r="R15" t="n">
-        <v>6928714</v>
+        <v>6928842</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2177,22 +2162,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120463172</v>
+        <v>120464085</v>
       </c>
       <c r="B16" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2205,34 +2190,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>376427</v>
+        <v>376731</v>
       </c>
       <c r="R16" t="n">
-        <v>6928969</v>
+        <v>6928890</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2291,10 +2276,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120462738</v>
+        <v>120462573</v>
       </c>
       <c r="B17" t="n">
-        <v>90594</v>
+        <v>74654</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2307,21 +2292,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1204</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2331,10 +2316,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>376546</v>
+        <v>376605</v>
       </c>
       <c r="R17" t="n">
-        <v>6928799</v>
+        <v>6928771</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2393,10 +2378,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120463824</v>
+        <v>120464355</v>
       </c>
       <c r="B18" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2409,21 +2394,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2433,10 +2418,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>376695</v>
+        <v>376822</v>
       </c>
       <c r="R18" t="n">
-        <v>6928830</v>
+        <v>6928965</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2495,10 +2480,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120464475</v>
+        <v>120463433</v>
       </c>
       <c r="B19" t="n">
-        <v>78542</v>
+        <v>78543</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2511,16 +2496,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2531,17 +2516,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>376903</v>
+        <v>376511</v>
       </c>
       <c r="R19" t="n">
-        <v>6928887</v>
+        <v>6928908</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2597,7 +2582,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120464038</v>
+        <v>120463133</v>
       </c>
       <c r="B20" t="n">
         <v>78542</v>
@@ -2637,10 +2622,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>376719</v>
+        <v>376426</v>
       </c>
       <c r="R20" t="n">
-        <v>6928860</v>
+        <v>6928956</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2699,10 +2684,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120463769</v>
+        <v>120462783</v>
       </c>
       <c r="B21" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2715,37 +2700,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>376666</v>
+        <v>376448</v>
       </c>
       <c r="R21" t="n">
-        <v>6928860</v>
+        <v>6928821</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2789,22 +2774,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120463188</v>
+        <v>120462709</v>
       </c>
       <c r="B22" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2817,34 +2802,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>376452</v>
+        <v>376574</v>
       </c>
       <c r="R22" t="n">
-        <v>6928954</v>
+        <v>6928783</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2903,10 +2888,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120462796</v>
+        <v>120463089</v>
       </c>
       <c r="B23" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2919,21 +2904,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2943,10 +2928,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>376500</v>
+        <v>376419</v>
       </c>
       <c r="R23" t="n">
-        <v>6928798</v>
+        <v>6928951</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3005,10 +2990,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120462344</v>
+        <v>120461918</v>
       </c>
       <c r="B24" t="n">
-        <v>90598</v>
+        <v>74654</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3021,21 +3006,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3045,10 +3030,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>376677</v>
+        <v>376774</v>
       </c>
       <c r="R24" t="n">
-        <v>6928749</v>
+        <v>6928741</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3107,10 +3092,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120461918</v>
+        <v>120463172</v>
       </c>
       <c r="B25" t="n">
-        <v>74654</v>
+        <v>90864</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3123,34 +3108,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>376774</v>
+        <v>376427</v>
       </c>
       <c r="R25" t="n">
-        <v>6928741</v>
+        <v>6928969</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3209,10 +3194,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120462917</v>
+        <v>120463512</v>
       </c>
       <c r="B26" t="n">
-        <v>78542</v>
+        <v>78543</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3225,16 +3210,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3249,13 +3234,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>376403</v>
+        <v>376585</v>
       </c>
       <c r="R26" t="n">
-        <v>6928904</v>
+        <v>6928865</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3311,10 +3296,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120462799</v>
+        <v>120461973</v>
       </c>
       <c r="B27" t="n">
-        <v>78543</v>
+        <v>74654</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3327,21 +3312,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>230405</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3351,13 +3336,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>376432</v>
+        <v>376741</v>
       </c>
       <c r="R27" t="n">
-        <v>6928842</v>
+        <v>6928740</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3401,22 +3386,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120464205</v>
+        <v>120461902</v>
       </c>
       <c r="B28" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3429,37 +3414,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>376778</v>
+        <v>376797</v>
       </c>
       <c r="R28" t="n">
-        <v>6928905</v>
+        <v>6928746</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3503,22 +3488,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120464355</v>
+        <v>120463914</v>
       </c>
       <c r="B29" t="n">
-        <v>78542</v>
+        <v>90576</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3531,34 +3516,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>376822</v>
+        <v>376684</v>
       </c>
       <c r="R29" t="n">
-        <v>6928965</v>
+        <v>6928823</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3617,10 +3602,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120463458</v>
+        <v>120464264</v>
       </c>
       <c r="B30" t="n">
-        <v>79624</v>
+        <v>90580</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3633,34 +3618,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>376530</v>
+        <v>376784</v>
       </c>
       <c r="R30" t="n">
-        <v>6928871</v>
+        <v>6928921</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3719,10 +3704,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120463009</v>
+        <v>120463650</v>
       </c>
       <c r="B31" t="n">
-        <v>78542</v>
+        <v>78641</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3735,34 +3720,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>376424</v>
+        <v>376627</v>
       </c>
       <c r="R31" t="n">
-        <v>6928913</v>
+        <v>6928864</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3821,10 +3806,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120464111</v>
+        <v>120462872</v>
       </c>
       <c r="B32" t="n">
-        <v>78542</v>
+        <v>78543</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3837,16 +3822,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3857,14 +3842,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>376700</v>
+        <v>376420</v>
       </c>
       <c r="R32" t="n">
-        <v>6928867</v>
+        <v>6928868</v>
       </c>
       <c r="S32" t="n">
         <v>3</v>
@@ -3923,10 +3908,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120462971</v>
+        <v>120462372</v>
       </c>
       <c r="B33" t="n">
-        <v>78543</v>
+        <v>78542</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3939,16 +3924,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3959,14 +3944,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>376410</v>
+        <v>376659</v>
       </c>
       <c r="R33" t="n">
-        <v>6928948</v>
+        <v>6928762</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
@@ -4025,10 +4010,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120462219</v>
+        <v>120463769</v>
       </c>
       <c r="B34" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4041,34 +4026,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>376700</v>
+        <v>376666</v>
       </c>
       <c r="R34" t="n">
-        <v>6928752</v>
+        <v>6928860</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4127,7 +4112,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120463773</v>
+        <v>120464210</v>
       </c>
       <c r="B35" t="n">
         <v>78542</v>
@@ -4163,17 +4148,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>376666</v>
+        <v>376763</v>
       </c>
       <c r="R35" t="n">
-        <v>6928860</v>
+        <v>6928949</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4217,22 +4202,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120461364</v>
+        <v>120462971</v>
       </c>
       <c r="B36" t="n">
-        <v>90580</v>
+        <v>78543</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4245,21 +4230,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>230405</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4269,13 +4254,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>376857</v>
+        <v>376410</v>
       </c>
       <c r="R36" t="n">
-        <v>6928677</v>
+        <v>6928948</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4319,19 +4304,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120462766</v>
+        <v>120464178</v>
       </c>
       <c r="B37" t="n">
         <v>78542</v>
@@ -4371,10 +4356,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>376533</v>
+        <v>376767</v>
       </c>
       <c r="R37" t="n">
-        <v>6928800</v>
+        <v>6928875</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4433,10 +4418,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120463512</v>
+        <v>120464397</v>
       </c>
       <c r="B38" t="n">
-        <v>78543</v>
+        <v>56532</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4445,41 +4430,56 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>230405</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>övernattning</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>376585</v>
+        <v>376843</v>
       </c>
       <c r="R38" t="n">
-        <v>6928865</v>
+        <v>6928942</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4523,22 +4523,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120464110</v>
+        <v>120462884</v>
       </c>
       <c r="B39" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4551,21 +4551,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4575,13 +4575,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>376748</v>
+        <v>376415</v>
       </c>
       <c r="R39" t="n">
-        <v>6928890</v>
+        <v>6928886</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4625,22 +4625,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120461419</v>
+        <v>120462634</v>
       </c>
       <c r="B40" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4653,37 +4653,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>376841</v>
+        <v>376605</v>
       </c>
       <c r="R40" t="n">
-        <v>6928719</v>
+        <v>6928771</v>
       </c>
       <c r="S40" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4727,22 +4727,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120462634</v>
+        <v>120462344</v>
       </c>
       <c r="B41" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4755,21 +4755,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4779,10 +4779,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>376605</v>
+        <v>376677</v>
       </c>
       <c r="R41" t="n">
-        <v>6928771</v>
+        <v>6928749</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4841,10 +4841,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120462911</v>
+        <v>120464383</v>
       </c>
       <c r="B42" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4857,37 +4857,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>376433</v>
+        <v>376836</v>
       </c>
       <c r="R42" t="n">
-        <v>6928842</v>
+        <v>6928949</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4931,22 +4931,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120462884</v>
+        <v>120463199</v>
       </c>
       <c r="B43" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4959,37 +4959,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>376415</v>
+        <v>376466</v>
       </c>
       <c r="R43" t="n">
-        <v>6928886</v>
+        <v>6928935</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5033,22 +5033,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120463679</v>
+        <v>120462773</v>
       </c>
       <c r="B44" t="n">
-        <v>90598</v>
+        <v>79624</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5061,21 +5061,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5085,13 +5085,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>376629</v>
+        <v>376533</v>
       </c>
       <c r="R44" t="n">
-        <v>6928862</v>
+        <v>6928800</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5135,19 +5135,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120462931</v>
+        <v>120461976</v>
       </c>
       <c r="B45" t="n">
         <v>78542</v>
@@ -5187,10 +5187,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>376436</v>
+        <v>376741</v>
       </c>
       <c r="R45" t="n">
-        <v>6928867</v>
+        <v>6928740</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5249,10 +5249,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120463133</v>
+        <v>120461364</v>
       </c>
       <c r="B46" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5265,21 +5265,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5289,10 +5289,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>376426</v>
+        <v>376857</v>
       </c>
       <c r="R46" t="n">
-        <v>6928956</v>
+        <v>6928677</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5351,10 +5351,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120463433</v>
+        <v>120461440</v>
       </c>
       <c r="B47" t="n">
-        <v>78543</v>
+        <v>79659</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5363,25 +5363,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>230405</v>
+        <v>6464</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5391,13 +5391,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>376511</v>
+        <v>376797</v>
       </c>
       <c r="R47" t="n">
-        <v>6928908</v>
+        <v>6928714</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5441,22 +5441,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120462877</v>
+        <v>120461838</v>
       </c>
       <c r="B48" t="n">
-        <v>74654</v>
+        <v>79624</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5469,37 +5469,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>376442</v>
+        <v>376813</v>
       </c>
       <c r="R48" t="n">
-        <v>6928809</v>
+        <v>6928747</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5543,19 +5543,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120464178</v>
+        <v>120462766</v>
       </c>
       <c r="B49" t="n">
         <v>78542</v>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>376767</v>
+        <v>376533</v>
       </c>
       <c r="R49" t="n">
-        <v>6928875</v>
+        <v>6928800</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5657,10 +5657,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120462773</v>
+        <v>120463009</v>
       </c>
       <c r="B50" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5673,21 +5673,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5697,10 +5697,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>376533</v>
+        <v>376424</v>
       </c>
       <c r="R50" t="n">
-        <v>6928800</v>
+        <v>6928913</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5759,10 +5759,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120463089</v>
+        <v>120463131</v>
       </c>
       <c r="B51" t="n">
-        <v>78542</v>
+        <v>78543</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5775,16 +5775,16 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5799,13 +5799,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>376419</v>
+        <v>376470</v>
       </c>
       <c r="R51" t="n">
-        <v>6928951</v>
+        <v>6928960</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5849,22 +5849,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120461440</v>
+        <v>120461861</v>
       </c>
       <c r="B52" t="n">
-        <v>79659</v>
+        <v>74654</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5873,25 +5873,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>376797</v>
+        <v>376772</v>
       </c>
       <c r="R52" t="n">
-        <v>6928714</v>
+        <v>6928732</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5963,7 +5963,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120461382</v>
+        <v>120461377</v>
       </c>
       <c r="B53" t="n">
         <v>79624</v>
@@ -5999,17 +5999,17 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>376842</v>
+        <v>376858</v>
       </c>
       <c r="R53" t="n">
-        <v>6928689</v>
+        <v>6928712</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6053,22 +6053,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120463175</v>
+        <v>120463679</v>
       </c>
       <c r="B54" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6081,37 +6081,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>376427</v>
+        <v>376629</v>
       </c>
       <c r="R54" t="n">
-        <v>6928969</v>
+        <v>6928862</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6155,22 +6155,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120462872</v>
+        <v>120462877</v>
       </c>
       <c r="B55" t="n">
-        <v>78543</v>
+        <v>74654</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6183,37 +6183,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>230405</v>
+        <v>6440</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>376420</v>
+        <v>376442</v>
       </c>
       <c r="R55" t="n">
-        <v>6928868</v>
+        <v>6928809</v>
       </c>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6257,22 +6257,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120462709</v>
+        <v>120462931</v>
       </c>
       <c r="B56" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6285,21 +6285,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6309,10 +6309,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>376574</v>
+        <v>376436</v>
       </c>
       <c r="R56" t="n">
-        <v>6928783</v>
+        <v>6928867</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6371,10 +6371,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120462573</v>
+        <v>120464110</v>
       </c>
       <c r="B57" t="n">
-        <v>74654</v>
+        <v>90598</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6387,21 +6387,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6411,10 +6411,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>376605</v>
+        <v>376748</v>
       </c>
       <c r="R57" t="n">
-        <v>6928771</v>
+        <v>6928890</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6473,10 +6473,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120463131</v>
+        <v>120464111</v>
       </c>
       <c r="B58" t="n">
-        <v>78543</v>
+        <v>78542</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6489,16 +6489,16 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6509,17 +6509,17 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>376470</v>
+        <v>376700</v>
       </c>
       <c r="R58" t="n">
-        <v>6928960</v>
+        <v>6928867</v>
       </c>
       <c r="S58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6575,10 +6575,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120464210</v>
+        <v>120464351</v>
       </c>
       <c r="B59" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6591,37 +6591,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>376763</v>
+        <v>376822</v>
       </c>
       <c r="R59" t="n">
-        <v>6928949</v>
+        <v>6928965</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6665,22 +6665,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120464085</v>
+        <v>120462738</v>
       </c>
       <c r="B60" t="n">
-        <v>78542</v>
+        <v>90594</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6693,21 +6693,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6717,10 +6717,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>376731</v>
+        <v>376546</v>
       </c>
       <c r="R60" t="n">
-        <v>6928890</v>
+        <v>6928799</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6779,10 +6779,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120463161</v>
+        <v>120463175</v>
       </c>
       <c r="B61" t="n">
-        <v>78543</v>
+        <v>90580</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6795,37 +6795,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>230405</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>376500</v>
+        <v>376427</v>
       </c>
       <c r="R61" t="n">
-        <v>6928936</v>
+        <v>6928969</v>
       </c>
       <c r="S61" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6869,22 +6869,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120463199</v>
+        <v>120462219</v>
       </c>
       <c r="B62" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6897,34 +6897,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>376466</v>
+        <v>376700</v>
       </c>
       <c r="R62" t="n">
-        <v>6928935</v>
+        <v>6928752</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6983,7 +6983,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120462783</v>
+        <v>120463773</v>
       </c>
       <c r="B63" t="n">
         <v>78542</v>
@@ -7019,17 +7019,17 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>376448</v>
+        <v>376666</v>
       </c>
       <c r="R63" t="n">
-        <v>6928821</v>
+        <v>6928860</v>
       </c>
       <c r="S63" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7073,22 +7073,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120461973</v>
+        <v>120461419</v>
       </c>
       <c r="B64" t="n">
-        <v>74654</v>
+        <v>79624</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7101,37 +7101,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>376741</v>
+        <v>376841</v>
       </c>
       <c r="R64" t="n">
-        <v>6928740</v>
+        <v>6928719</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7175,22 +7175,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120462372</v>
+        <v>120464020</v>
       </c>
       <c r="B65" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7203,21 +7203,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7227,10 +7227,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>376659</v>
+        <v>376688</v>
       </c>
       <c r="R65" t="n">
-        <v>6928762</v>
+        <v>6928842</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -7289,10 +7289,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120461377</v>
+        <v>120463768</v>
       </c>
       <c r="B66" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7305,34 +7305,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>376858</v>
+        <v>376653</v>
       </c>
       <c r="R66" t="n">
-        <v>6928712</v>
+        <v>6928851</v>
       </c>
       <c r="S66" t="n">
         <v>4</v>
@@ -7391,10 +7391,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120461861</v>
+        <v>120461382</v>
       </c>
       <c r="B67" t="n">
-        <v>74654</v>
+        <v>79624</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7407,21 +7407,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7431,10 +7431,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>376772</v>
+        <v>376842</v>
       </c>
       <c r="R67" t="n">
-        <v>6928732</v>
+        <v>6928689</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7493,10 +7493,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120461976</v>
+        <v>120464205</v>
       </c>
       <c r="B68" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7509,21 +7509,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7533,10 +7533,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>376741</v>
+        <v>376778</v>
       </c>
       <c r="R68" t="n">
-        <v>6928740</v>
+        <v>6928905</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7595,10 +7595,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120464020</v>
+        <v>120464475</v>
       </c>
       <c r="B69" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7611,21 +7611,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7635,10 +7635,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>376688</v>
+        <v>376903</v>
       </c>
       <c r="R69" t="n">
-        <v>6928842</v>
+        <v>6928887</v>
       </c>
       <c r="S69" t="n">
         <v>4</v>
@@ -7697,10 +7697,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120463650</v>
+        <v>120461553</v>
       </c>
       <c r="B70" t="n">
-        <v>78641</v>
+        <v>79624</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7713,34 +7713,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>967</v>
+        <v>2081</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>376627</v>
+        <v>376797</v>
       </c>
       <c r="R70" t="n">
-        <v>6928864</v>
+        <v>6928714</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7799,7 +7799,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120464264</v>
+        <v>120464218</v>
       </c>
       <c r="B71" t="n">
         <v>90580</v>
@@ -7839,10 +7839,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>376784</v>
+        <v>376778</v>
       </c>
       <c r="R71" t="n">
-        <v>6928921</v>
+        <v>6928905</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7901,10 +7901,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120463768</v>
+        <v>120463161</v>
       </c>
       <c r="B72" t="n">
-        <v>78542</v>
+        <v>78543</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7917,16 +7917,16 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -7941,13 +7941,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>376653</v>
+        <v>376500</v>
       </c>
       <c r="R72" t="n">
-        <v>6928851</v>
+        <v>6928936</v>
       </c>
       <c r="S72" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8003,10 +8003,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120463914</v>
+        <v>120463188</v>
       </c>
       <c r="B73" t="n">
-        <v>90576</v>
+        <v>78542</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8019,21 +8019,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>376684</v>
+        <v>376452</v>
       </c>
       <c r="R73" t="n">
-        <v>6928823</v>
+        <v>6928954</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8105,10 +8105,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120461838</v>
+        <v>120461491</v>
       </c>
       <c r="B74" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8121,37 +8121,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>376813</v>
+        <v>376797</v>
       </c>
       <c r="R74" t="n">
-        <v>6928747</v>
+        <v>6928714</v>
       </c>
       <c r="S74" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8195,12 +8195,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>

--- a/artfynd/A 38064-2024 artfynd.xlsx
+++ b/artfynd/A 38064-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120315938</v>
+        <v>120315897</v>
       </c>
       <c r="B2" t="n">
         <v>57320</v>
@@ -708,12 +708,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -723,10 +731,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>376753</v>
+        <v>376875</v>
       </c>
       <c r="R2" t="n">
-        <v>6928863</v>
+        <v>6928715</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,6 +767,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Observerad under flera tillfällen under besöket</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,7 +798,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120315910</v>
+        <v>120315903</v>
       </c>
       <c r="B3" t="n">
         <v>57320</v>
@@ -833,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>376797</v>
+        <v>376869</v>
       </c>
       <c r="R3" t="n">
-        <v>6928695</v>
+        <v>6928711</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,7 +908,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120315897</v>
+        <v>120315938</v>
       </c>
       <c r="B4" t="n">
         <v>57320</v>
@@ -928,20 +941,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -951,10 +956,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>376875</v>
+        <v>376753</v>
       </c>
       <c r="R4" t="n">
-        <v>6928715</v>
+        <v>6928863</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,11 +992,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-09</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Observerad under flera tillfällen under besöket</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120315911</v>
+        <v>120315910</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,26 +1034,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1099,18 +1104,12 @@
           <t>2024-10-09</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Flera platser i området</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1240,7 +1239,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120315903</v>
+        <v>120315914</v>
       </c>
       <c r="B7" t="n">
         <v>57320</v>
@@ -1288,10 +1287,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>376869</v>
+        <v>376706</v>
       </c>
       <c r="R7" t="n">
-        <v>6928711</v>
+        <v>6928747</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1350,10 +1349,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120315914</v>
+        <v>120315911</v>
       </c>
       <c r="B8" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1366,31 +1365,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1398,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>376706</v>
+        <v>376797</v>
       </c>
       <c r="R8" t="n">
-        <v>6928747</v>
+        <v>6928695</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1436,12 +1430,18 @@
           <t>2024-10-09</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Flera platser i området</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120462911</v>
+        <v>120464397</v>
       </c>
       <c r="B9" t="n">
-        <v>90580</v>
+        <v>56532</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1472,41 +1472,56 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>övernattning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>376433</v>
+        <v>376843</v>
       </c>
       <c r="R9" t="n">
-        <v>6928842</v>
+        <v>6928942</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1562,10 +1577,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120462796</v>
+        <v>120464218</v>
       </c>
       <c r="B10" t="n">
-        <v>74654</v>
+        <v>90580</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1578,21 +1593,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1602,10 +1617,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>376500</v>
+        <v>376778</v>
       </c>
       <c r="R10" t="n">
-        <v>6928798</v>
+        <v>6928905</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1664,10 +1679,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120463824</v>
+        <v>120461364</v>
       </c>
       <c r="B11" t="n">
-        <v>74654</v>
+        <v>90580</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1680,21 +1695,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1704,10 +1719,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>376695</v>
+        <v>376857</v>
       </c>
       <c r="R11" t="n">
-        <v>6928830</v>
+        <v>6928677</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1766,10 +1781,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120463458</v>
+        <v>120462872</v>
       </c>
       <c r="B12" t="n">
-        <v>79624</v>
+        <v>78543</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1782,37 +1797,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>230405</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>376530</v>
+        <v>376420</v>
       </c>
       <c r="R12" t="n">
-        <v>6928871</v>
+        <v>6928868</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1856,22 +1871,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120464038</v>
+        <v>120461861</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1884,21 +1899,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1908,10 +1923,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>376719</v>
+        <v>376772</v>
       </c>
       <c r="R13" t="n">
-        <v>6928860</v>
+        <v>6928732</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1970,10 +1985,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120462917</v>
+        <v>120462877</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1986,37 +2001,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>376403</v>
+        <v>376442</v>
       </c>
       <c r="R14" t="n">
-        <v>6928904</v>
+        <v>6928809</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2060,22 +2075,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120462799</v>
+        <v>120463172</v>
       </c>
       <c r="B15" t="n">
-        <v>78543</v>
+        <v>90864</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2088,37 +2103,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>230405</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>376432</v>
+        <v>376427</v>
       </c>
       <c r="R15" t="n">
-        <v>6928842</v>
+        <v>6928969</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2162,22 +2177,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120464085</v>
+        <v>120461377</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2190,37 +2205,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>376731</v>
+        <v>376858</v>
       </c>
       <c r="R16" t="n">
-        <v>6928890</v>
+        <v>6928712</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2264,22 +2279,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120462573</v>
+        <v>120462372</v>
       </c>
       <c r="B17" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2292,37 +2307,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>376605</v>
+        <v>376659</v>
       </c>
       <c r="R17" t="n">
-        <v>6928771</v>
+        <v>6928762</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2366,19 +2381,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120464355</v>
+        <v>120463133</v>
       </c>
       <c r="B18" t="n">
         <v>78542</v>
@@ -2418,10 +2433,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>376822</v>
+        <v>376426</v>
       </c>
       <c r="R18" t="n">
-        <v>6928965</v>
+        <v>6928956</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2480,10 +2495,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120463433</v>
+        <v>120464111</v>
       </c>
       <c r="B19" t="n">
-        <v>78543</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2496,16 +2511,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2516,14 +2531,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>376511</v>
+        <v>376700</v>
       </c>
       <c r="R19" t="n">
-        <v>6928908</v>
+        <v>6928867</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
@@ -2582,7 +2597,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120463133</v>
+        <v>120462917</v>
       </c>
       <c r="B20" t="n">
         <v>78542</v>
@@ -2622,13 +2637,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>376426</v>
+        <v>376403</v>
       </c>
       <c r="R20" t="n">
-        <v>6928956</v>
+        <v>6928904</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2672,19 +2687,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120462783</v>
+        <v>120464475</v>
       </c>
       <c r="B21" t="n">
         <v>78542</v>
@@ -2724,13 +2739,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>376448</v>
+        <v>376903</v>
       </c>
       <c r="R21" t="n">
-        <v>6928821</v>
+        <v>6928887</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2786,10 +2801,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120462709</v>
+        <v>120463769</v>
       </c>
       <c r="B22" t="n">
-        <v>90598</v>
+        <v>74654</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2802,34 +2817,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>376574</v>
+        <v>376666</v>
       </c>
       <c r="R22" t="n">
-        <v>6928783</v>
+        <v>6928860</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2888,7 +2903,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120463089</v>
+        <v>120462783</v>
       </c>
       <c r="B23" t="n">
         <v>78542</v>
@@ -2924,17 +2939,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>376419</v>
+        <v>376448</v>
       </c>
       <c r="R23" t="n">
-        <v>6928951</v>
+        <v>6928821</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2978,22 +2993,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120461918</v>
+        <v>120462884</v>
       </c>
       <c r="B24" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3006,21 +3021,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3030,13 +3045,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>376774</v>
+        <v>376415</v>
       </c>
       <c r="R24" t="n">
-        <v>6928741</v>
+        <v>6928886</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3080,22 +3095,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120463172</v>
+        <v>120461382</v>
       </c>
       <c r="B25" t="n">
-        <v>90864</v>
+        <v>79624</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3108,34 +3123,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>376427</v>
+        <v>376842</v>
       </c>
       <c r="R25" t="n">
-        <v>6928969</v>
+        <v>6928689</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3194,10 +3209,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120463512</v>
+        <v>120463824</v>
       </c>
       <c r="B26" t="n">
-        <v>78543</v>
+        <v>74654</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3210,21 +3225,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>230405</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3234,13 +3249,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>376585</v>
+        <v>376695</v>
       </c>
       <c r="R26" t="n">
-        <v>6928865</v>
+        <v>6928830</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3284,22 +3299,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120461973</v>
+        <v>120464038</v>
       </c>
       <c r="B27" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3312,21 +3327,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3336,10 +3351,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>376741</v>
+        <v>376719</v>
       </c>
       <c r="R27" t="n">
-        <v>6928740</v>
+        <v>6928860</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3398,10 +3413,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120461902</v>
+        <v>120462971</v>
       </c>
       <c r="B28" t="n">
-        <v>78542</v>
+        <v>78543</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3414,16 +3429,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3434,14 +3449,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>376797</v>
+        <v>376410</v>
       </c>
       <c r="R28" t="n">
-        <v>6928746</v>
+        <v>6928948</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3500,10 +3515,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120463914</v>
+        <v>120462911</v>
       </c>
       <c r="B29" t="n">
-        <v>90576</v>
+        <v>90580</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3516,21 +3531,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3540,10 +3555,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>376684</v>
+        <v>376433</v>
       </c>
       <c r="R29" t="n">
-        <v>6928823</v>
+        <v>6928842</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3602,10 +3617,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120464264</v>
+        <v>120464178</v>
       </c>
       <c r="B30" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3618,21 +3633,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3642,10 +3657,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>376784</v>
+        <v>376767</v>
       </c>
       <c r="R30" t="n">
-        <v>6928921</v>
+        <v>6928875</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3704,10 +3719,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120463650</v>
+        <v>120464351</v>
       </c>
       <c r="B31" t="n">
-        <v>78641</v>
+        <v>74654</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3720,34 +3735,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>967</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>376627</v>
+        <v>376822</v>
       </c>
       <c r="R31" t="n">
-        <v>6928864</v>
+        <v>6928965</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3806,10 +3821,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120462872</v>
+        <v>120461976</v>
       </c>
       <c r="B32" t="n">
-        <v>78543</v>
+        <v>78542</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3822,16 +3837,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3846,13 +3861,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>376420</v>
+        <v>376741</v>
       </c>
       <c r="R32" t="n">
-        <v>6928868</v>
+        <v>6928740</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3896,19 +3911,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120462372</v>
+        <v>120462766</v>
       </c>
       <c r="B33" t="n">
         <v>78542</v>
@@ -3944,17 +3959,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>376659</v>
+        <v>376533</v>
       </c>
       <c r="R33" t="n">
-        <v>6928762</v>
+        <v>6928800</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3998,22 +4013,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120463769</v>
+        <v>120463768</v>
       </c>
       <c r="B34" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4026,37 +4041,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>376666</v>
+        <v>376653</v>
       </c>
       <c r="R34" t="n">
-        <v>6928860</v>
+        <v>6928851</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4100,22 +4115,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120464210</v>
+        <v>120462573</v>
       </c>
       <c r="B35" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4128,37 +4143,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>376763</v>
+        <v>376605</v>
       </c>
       <c r="R35" t="n">
-        <v>6928949</v>
+        <v>6928771</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4202,22 +4217,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120462971</v>
+        <v>120461902</v>
       </c>
       <c r="B36" t="n">
-        <v>78543</v>
+        <v>78542</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4230,16 +4245,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4250,14 +4265,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>376410</v>
+        <v>376797</v>
       </c>
       <c r="R36" t="n">
-        <v>6928948</v>
+        <v>6928746</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4316,10 +4331,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120464178</v>
+        <v>120462796</v>
       </c>
       <c r="B37" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4332,21 +4347,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4356,10 +4371,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>376767</v>
+        <v>376500</v>
       </c>
       <c r="R37" t="n">
-        <v>6928875</v>
+        <v>6928798</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4418,10 +4433,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120464397</v>
+        <v>120464085</v>
       </c>
       <c r="B38" t="n">
-        <v>56532</v>
+        <v>78542</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4430,56 +4445,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>övernattning</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>376843</v>
+        <v>376731</v>
       </c>
       <c r="R38" t="n">
-        <v>6928942</v>
+        <v>6928890</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4535,10 +4535,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120462884</v>
+        <v>120461838</v>
       </c>
       <c r="B39" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4551,37 +4551,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>376415</v>
+        <v>376813</v>
       </c>
       <c r="R39" t="n">
-        <v>6928886</v>
+        <v>6928747</v>
       </c>
       <c r="S39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4637,10 +4637,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120462634</v>
+        <v>120464110</v>
       </c>
       <c r="B40" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4653,21 +4653,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4677,10 +4677,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>376605</v>
+        <v>376748</v>
       </c>
       <c r="R40" t="n">
-        <v>6928771</v>
+        <v>6928890</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4739,10 +4739,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120462344</v>
+        <v>120463009</v>
       </c>
       <c r="B41" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4755,21 +4755,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4779,10 +4779,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>376677</v>
+        <v>376424</v>
       </c>
       <c r="R41" t="n">
-        <v>6928749</v>
+        <v>6928913</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4841,10 +4841,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120464383</v>
+        <v>120463679</v>
       </c>
       <c r="B42" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4857,34 +4857,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>376836</v>
+        <v>376629</v>
       </c>
       <c r="R42" t="n">
-        <v>6928949</v>
+        <v>6928862</v>
       </c>
       <c r="S42" t="n">
         <v>3</v>
@@ -5147,7 +5147,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120461976</v>
+        <v>120463089</v>
       </c>
       <c r="B45" t="n">
         <v>78542</v>
@@ -5187,10 +5187,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>376741</v>
+        <v>376419</v>
       </c>
       <c r="R45" t="n">
-        <v>6928740</v>
+        <v>6928951</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5249,10 +5249,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120461364</v>
+        <v>120463188</v>
       </c>
       <c r="B46" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5265,34 +5265,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>376857</v>
+        <v>376452</v>
       </c>
       <c r="R46" t="n">
-        <v>6928677</v>
+        <v>6928954</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5351,10 +5351,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120461440</v>
+        <v>120463458</v>
       </c>
       <c r="B47" t="n">
-        <v>79659</v>
+        <v>79624</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5363,38 +5363,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>376797</v>
+        <v>376530</v>
       </c>
       <c r="R47" t="n">
-        <v>6928714</v>
+        <v>6928871</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5453,10 +5453,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120461838</v>
+        <v>120464355</v>
       </c>
       <c r="B48" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5469,37 +5469,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>376813</v>
+        <v>376822</v>
       </c>
       <c r="R48" t="n">
-        <v>6928747</v>
+        <v>6928965</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5543,22 +5543,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120462766</v>
+        <v>120463433</v>
       </c>
       <c r="B49" t="n">
-        <v>78542</v>
+        <v>78543</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5571,16 +5571,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5595,13 +5595,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>376533</v>
+        <v>376511</v>
       </c>
       <c r="R49" t="n">
-        <v>6928800</v>
+        <v>6928908</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5645,19 +5645,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120463009</v>
+        <v>120464210</v>
       </c>
       <c r="B50" t="n">
         <v>78542</v>
@@ -5693,17 +5693,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>376424</v>
+        <v>376763</v>
       </c>
       <c r="R50" t="n">
-        <v>6928913</v>
+        <v>6928949</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5747,22 +5747,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120463131</v>
+        <v>120461419</v>
       </c>
       <c r="B51" t="n">
-        <v>78543</v>
+        <v>79624</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5775,34 +5775,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>230405</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>376470</v>
+        <v>376841</v>
       </c>
       <c r="R51" t="n">
-        <v>6928960</v>
+        <v>6928719</v>
       </c>
       <c r="S51" t="n">
         <v>4</v>
@@ -5861,10 +5861,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120461861</v>
+        <v>120463650</v>
       </c>
       <c r="B52" t="n">
-        <v>74654</v>
+        <v>78641</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5877,34 +5877,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>967</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>376772</v>
+        <v>376627</v>
       </c>
       <c r="R52" t="n">
-        <v>6928732</v>
+        <v>6928864</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5963,10 +5963,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120461377</v>
+        <v>120461440</v>
       </c>
       <c r="B53" t="n">
-        <v>79624</v>
+        <v>79659</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5975,41 +5975,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>376858</v>
+        <v>376797</v>
       </c>
       <c r="R53" t="n">
-        <v>6928712</v>
+        <v>6928714</v>
       </c>
       <c r="S53" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6053,22 +6053,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120463679</v>
+        <v>120464264</v>
       </c>
       <c r="B54" t="n">
-        <v>90598</v>
+        <v>90580</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6081,21 +6081,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6105,13 +6105,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>376629</v>
+        <v>376784</v>
       </c>
       <c r="R54" t="n">
-        <v>6928862</v>
+        <v>6928921</v>
       </c>
       <c r="S54" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6155,22 +6155,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120462877</v>
+        <v>120462219</v>
       </c>
       <c r="B55" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6183,34 +6183,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>376442</v>
+        <v>376700</v>
       </c>
       <c r="R55" t="n">
-        <v>6928809</v>
+        <v>6928752</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6269,10 +6269,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120462931</v>
+        <v>120464020</v>
       </c>
       <c r="B56" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6285,37 +6285,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>376436</v>
+        <v>376688</v>
       </c>
       <c r="R56" t="n">
-        <v>6928867</v>
+        <v>6928842</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6359,22 +6359,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120464110</v>
+        <v>120461491</v>
       </c>
       <c r="B57" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6387,21 +6387,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6411,10 +6411,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>376748</v>
+        <v>376797</v>
       </c>
       <c r="R57" t="n">
-        <v>6928890</v>
+        <v>6928714</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6473,7 +6473,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120464111</v>
+        <v>120464383</v>
       </c>
       <c r="B58" t="n">
         <v>78542</v>
@@ -6513,10 +6513,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>376700</v>
+        <v>376836</v>
       </c>
       <c r="R58" t="n">
-        <v>6928867</v>
+        <v>6928949</v>
       </c>
       <c r="S58" t="n">
         <v>3</v>
@@ -6575,10 +6575,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120464351</v>
+        <v>120463914</v>
       </c>
       <c r="B59" t="n">
-        <v>74654</v>
+        <v>90576</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6591,34 +6591,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>376822</v>
+        <v>376684</v>
       </c>
       <c r="R59" t="n">
-        <v>6928965</v>
+        <v>6928823</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6677,10 +6677,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120462738</v>
+        <v>120461553</v>
       </c>
       <c r="B60" t="n">
-        <v>90594</v>
+        <v>79624</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6693,21 +6693,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6717,10 +6717,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>376546</v>
+        <v>376797</v>
       </c>
       <c r="R60" t="n">
-        <v>6928799</v>
+        <v>6928714</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6779,10 +6779,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120463175</v>
+        <v>120464205</v>
       </c>
       <c r="B61" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6795,34 +6795,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>376427</v>
+        <v>376778</v>
       </c>
       <c r="R61" t="n">
-        <v>6928969</v>
+        <v>6928905</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6881,7 +6881,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120462219</v>
+        <v>120462634</v>
       </c>
       <c r="B62" t="n">
         <v>78542</v>
@@ -6921,10 +6921,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>376700</v>
+        <v>376605</v>
       </c>
       <c r="R62" t="n">
-        <v>6928752</v>
+        <v>6928771</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6983,10 +6983,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120463773</v>
+        <v>120462709</v>
       </c>
       <c r="B63" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6999,34 +6999,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>376666</v>
+        <v>376574</v>
       </c>
       <c r="R63" t="n">
-        <v>6928860</v>
+        <v>6928783</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7085,10 +7085,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120461419</v>
+        <v>120461973</v>
       </c>
       <c r="B64" t="n">
-        <v>79624</v>
+        <v>74654</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7101,37 +7101,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>376841</v>
+        <v>376741</v>
       </c>
       <c r="R64" t="n">
-        <v>6928719</v>
+        <v>6928740</v>
       </c>
       <c r="S64" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7175,22 +7175,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120464020</v>
+        <v>120462344</v>
       </c>
       <c r="B65" t="n">
-        <v>79624</v>
+        <v>90598</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7203,37 +7203,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>376688</v>
+        <v>376677</v>
       </c>
       <c r="R65" t="n">
-        <v>6928842</v>
+        <v>6928749</v>
       </c>
       <c r="S65" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7277,22 +7277,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120463768</v>
+        <v>120463175</v>
       </c>
       <c r="B66" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7305,37 +7305,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>376653</v>
+        <v>376427</v>
       </c>
       <c r="R66" t="n">
-        <v>6928851</v>
+        <v>6928969</v>
       </c>
       <c r="S66" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7379,22 +7379,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120461382</v>
+        <v>120462738</v>
       </c>
       <c r="B67" t="n">
-        <v>79624</v>
+        <v>90594</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7407,21 +7407,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7431,10 +7431,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>376842</v>
+        <v>376546</v>
       </c>
       <c r="R67" t="n">
-        <v>6928689</v>
+        <v>6928799</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7493,10 +7493,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120464205</v>
+        <v>120463131</v>
       </c>
       <c r="B68" t="n">
-        <v>90598</v>
+        <v>78543</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7509,21 +7509,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5432</v>
+        <v>230405</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7533,13 +7533,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>376778</v>
+        <v>376470</v>
       </c>
       <c r="R68" t="n">
-        <v>6928905</v>
+        <v>6928960</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7583,22 +7583,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120464475</v>
+        <v>120463161</v>
       </c>
       <c r="B69" t="n">
-        <v>78542</v>
+        <v>78543</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7611,16 +7611,16 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -7631,17 +7631,17 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>376903</v>
+        <v>376500</v>
       </c>
       <c r="R69" t="n">
-        <v>6928887</v>
+        <v>6928936</v>
       </c>
       <c r="S69" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7697,10 +7697,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120461553</v>
+        <v>120462799</v>
       </c>
       <c r="B70" t="n">
-        <v>79624</v>
+        <v>78543</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7713,21 +7713,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2081</v>
+        <v>230405</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7737,13 +7737,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>376797</v>
+        <v>376432</v>
       </c>
       <c r="R70" t="n">
-        <v>6928714</v>
+        <v>6928842</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7787,22 +7787,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120464218</v>
+        <v>120461918</v>
       </c>
       <c r="B71" t="n">
-        <v>90580</v>
+        <v>74654</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7815,21 +7815,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7839,10 +7839,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>376778</v>
+        <v>376774</v>
       </c>
       <c r="R71" t="n">
-        <v>6928905</v>
+        <v>6928741</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7901,10 +7901,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120463161</v>
+        <v>120463773</v>
       </c>
       <c r="B72" t="n">
-        <v>78543</v>
+        <v>78542</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7917,16 +7917,16 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -7937,17 +7937,17 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>376500</v>
+        <v>376666</v>
       </c>
       <c r="R72" t="n">
-        <v>6928936</v>
+        <v>6928860</v>
       </c>
       <c r="S72" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7991,19 +7991,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120463188</v>
+        <v>120462931</v>
       </c>
       <c r="B73" t="n">
         <v>78542</v>
@@ -8039,14 +8039,14 @@
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>376452</v>
+        <v>376436</v>
       </c>
       <c r="R73" t="n">
-        <v>6928954</v>
+        <v>6928867</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8105,10 +8105,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120461491</v>
+        <v>120463512</v>
       </c>
       <c r="B74" t="n">
-        <v>78542</v>
+        <v>78543</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8121,16 +8121,16 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -8145,13 +8145,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>376797</v>
+        <v>376585</v>
       </c>
       <c r="R74" t="n">
-        <v>6928714</v>
+        <v>6928865</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8195,12 +8195,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>

--- a/artfynd/A 38064-2024 artfynd.xlsx
+++ b/artfynd/A 38064-2024 artfynd.xlsx
@@ -2801,10 +2801,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120463769</v>
+        <v>120461382</v>
       </c>
       <c r="B22" t="n">
-        <v>74654</v>
+        <v>79624</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2817,34 +2817,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>376666</v>
+        <v>376842</v>
       </c>
       <c r="R22" t="n">
-        <v>6928860</v>
+        <v>6928689</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2903,10 +2903,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120462783</v>
+        <v>120463769</v>
       </c>
       <c r="B23" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2919,37 +2919,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>376448</v>
+        <v>376666</v>
       </c>
       <c r="R23" t="n">
-        <v>6928821</v>
+        <v>6928860</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2993,19 +2993,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120462884</v>
+        <v>120462783</v>
       </c>
       <c r="B24" t="n">
         <v>78542</v>
@@ -3041,17 +3041,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>376415</v>
+        <v>376448</v>
       </c>
       <c r="R24" t="n">
-        <v>6928886</v>
+        <v>6928821</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3107,10 +3107,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120461382</v>
+        <v>120462884</v>
       </c>
       <c r="B25" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3123,21 +3123,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3147,13 +3147,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>376842</v>
+        <v>376415</v>
       </c>
       <c r="R25" t="n">
-        <v>6928689</v>
+        <v>6928886</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3197,12 +3197,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -6575,10 +6575,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120463914</v>
+        <v>120464205</v>
       </c>
       <c r="B59" t="n">
-        <v>90576</v>
+        <v>90598</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6591,34 +6591,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>376684</v>
+        <v>376778</v>
       </c>
       <c r="R59" t="n">
-        <v>6928823</v>
+        <v>6928905</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6677,10 +6677,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120461553</v>
+        <v>120462634</v>
       </c>
       <c r="B60" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6693,21 +6693,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6717,10 +6717,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>376797</v>
+        <v>376605</v>
       </c>
       <c r="R60" t="n">
-        <v>6928714</v>
+        <v>6928771</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6779,7 +6779,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120464205</v>
+        <v>120462709</v>
       </c>
       <c r="B61" t="n">
         <v>90598</v>
@@ -6819,10 +6819,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>376778</v>
+        <v>376574</v>
       </c>
       <c r="R61" t="n">
-        <v>6928905</v>
+        <v>6928783</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6881,10 +6881,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120462634</v>
+        <v>120463914</v>
       </c>
       <c r="B62" t="n">
-        <v>78542</v>
+        <v>90576</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6897,34 +6897,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>376605</v>
+        <v>376684</v>
       </c>
       <c r="R62" t="n">
-        <v>6928771</v>
+        <v>6928823</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6983,10 +6983,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120462709</v>
+        <v>120461553</v>
       </c>
       <c r="B63" t="n">
-        <v>90598</v>
+        <v>79624</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6999,21 +6999,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7023,10 +7023,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>376574</v>
+        <v>376797</v>
       </c>
       <c r="R63" t="n">
-        <v>6928783</v>
+        <v>6928714</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>

--- a/artfynd/A 38064-2024 artfynd.xlsx
+++ b/artfynd/A 38064-2024 artfynd.xlsx
@@ -1018,7 +1018,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120315910</v>
+        <v>120315914</v>
       </c>
       <c r="B5" t="n">
         <v>57320</v>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>376797</v>
+        <v>376706</v>
       </c>
       <c r="R5" t="n">
-        <v>6928695</v>
+        <v>6928747</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1239,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120315914</v>
+        <v>120315911</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1255,31 +1255,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1287,10 +1282,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>376706</v>
+        <v>376797</v>
       </c>
       <c r="R7" t="n">
-        <v>6928747</v>
+        <v>6928695</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,12 +1320,18 @@
           <t>2024-10-09</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Flera platser i området</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1349,10 +1350,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120315911</v>
+        <v>120315910</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1365,26 +1366,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1430,18 +1436,12 @@
           <t>2024-10-09</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Flera platser i området</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120464397</v>
+        <v>120462573</v>
       </c>
       <c r="B9" t="n">
-        <v>56532</v>
+        <v>74654</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1472,56 +1472,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>övernattning</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>376843</v>
+        <v>376605</v>
       </c>
       <c r="R9" t="n">
-        <v>6928942</v>
+        <v>6928771</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1577,10 +1562,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120464218</v>
+        <v>120464475</v>
       </c>
       <c r="B10" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1593,37 +1578,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>376778</v>
+        <v>376903</v>
       </c>
       <c r="R10" t="n">
-        <v>6928905</v>
+        <v>6928887</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1667,22 +1652,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120461364</v>
+        <v>120462344</v>
       </c>
       <c r="B11" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1695,21 +1680,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1719,10 +1704,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>376857</v>
+        <v>376677</v>
       </c>
       <c r="R11" t="n">
-        <v>6928677</v>
+        <v>6928749</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1781,10 +1766,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120462872</v>
+        <v>120463458</v>
       </c>
       <c r="B12" t="n">
-        <v>78543</v>
+        <v>79624</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1797,37 +1782,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>230405</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>376420</v>
+        <v>376530</v>
       </c>
       <c r="R12" t="n">
-        <v>6928868</v>
+        <v>6928871</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1871,22 +1856,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120461861</v>
+        <v>120464397</v>
       </c>
       <c r="B13" t="n">
-        <v>74654</v>
+        <v>56532</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1895,41 +1880,56 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>övernattning</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>376772</v>
+        <v>376843</v>
       </c>
       <c r="R13" t="n">
-        <v>6928732</v>
+        <v>6928942</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1985,10 +1985,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120462877</v>
+        <v>120462884</v>
       </c>
       <c r="B14" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2001,37 +2001,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>376442</v>
+        <v>376415</v>
       </c>
       <c r="R14" t="n">
-        <v>6928809</v>
+        <v>6928886</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2075,22 +2075,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120463172</v>
+        <v>120463650</v>
       </c>
       <c r="B15" t="n">
-        <v>90864</v>
+        <v>78641</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2103,21 +2103,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>967</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>376427</v>
+        <v>376627</v>
       </c>
       <c r="R15" t="n">
-        <v>6928969</v>
+        <v>6928864</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2189,10 +2189,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120461377</v>
+        <v>120462796</v>
       </c>
       <c r="B16" t="n">
-        <v>79624</v>
+        <v>74654</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2205,37 +2205,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>376858</v>
+        <v>376500</v>
       </c>
       <c r="R16" t="n">
-        <v>6928712</v>
+        <v>6928798</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2279,22 +2279,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120462372</v>
+        <v>120461419</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2307,21 +2307,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2331,10 +2331,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>376659</v>
+        <v>376841</v>
       </c>
       <c r="R17" t="n">
-        <v>6928762</v>
+        <v>6928719</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2393,10 +2393,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120463133</v>
+        <v>120462773</v>
       </c>
       <c r="B18" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2409,21 +2409,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>376426</v>
+        <v>376533</v>
       </c>
       <c r="R18" t="n">
-        <v>6928956</v>
+        <v>6928800</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2495,10 +2495,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120464111</v>
+        <v>120461382</v>
       </c>
       <c r="B19" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2511,37 +2511,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>376700</v>
+        <v>376842</v>
       </c>
       <c r="R19" t="n">
-        <v>6928867</v>
+        <v>6928689</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2585,22 +2585,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120462917</v>
+        <v>120461377</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2613,37 +2613,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>376403</v>
+        <v>376858</v>
       </c>
       <c r="R20" t="n">
-        <v>6928904</v>
+        <v>6928712</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2699,10 +2699,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120464475</v>
+        <v>120463512</v>
       </c>
       <c r="B21" t="n">
-        <v>78542</v>
+        <v>78543</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2715,16 +2715,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2735,17 +2735,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>376903</v>
+        <v>376585</v>
       </c>
       <c r="R21" t="n">
-        <v>6928887</v>
+        <v>6928865</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2801,10 +2801,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120461382</v>
+        <v>120464355</v>
       </c>
       <c r="B22" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2817,21 +2817,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2841,10 +2841,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>376842</v>
+        <v>376822</v>
       </c>
       <c r="R22" t="n">
-        <v>6928689</v>
+        <v>6928965</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2903,10 +2903,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120463769</v>
+        <v>120463188</v>
       </c>
       <c r="B23" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2919,21 +2919,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2943,10 +2943,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>376666</v>
+        <v>376452</v>
       </c>
       <c r="R23" t="n">
-        <v>6928860</v>
+        <v>6928954</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3005,10 +3005,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120462783</v>
+        <v>120463679</v>
       </c>
       <c r="B24" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3021,34 +3021,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>376448</v>
+        <v>376629</v>
       </c>
       <c r="R24" t="n">
-        <v>6928821</v>
+        <v>6928862</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
@@ -3107,10 +3107,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120462884</v>
+        <v>120463175</v>
       </c>
       <c r="B25" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3123,37 +3123,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>376415</v>
+        <v>376427</v>
       </c>
       <c r="R25" t="n">
-        <v>6928886</v>
+        <v>6928969</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3197,22 +3197,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120463824</v>
+        <v>120464085</v>
       </c>
       <c r="B26" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3225,21 +3225,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>376695</v>
+        <v>376731</v>
       </c>
       <c r="R26" t="n">
-        <v>6928830</v>
+        <v>6928890</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3311,7 +3311,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120464038</v>
+        <v>120462931</v>
       </c>
       <c r="B27" t="n">
         <v>78542</v>
@@ -3351,10 +3351,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>376719</v>
+        <v>376436</v>
       </c>
       <c r="R27" t="n">
-        <v>6928860</v>
+        <v>6928867</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3413,7 +3413,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120462971</v>
+        <v>120463433</v>
       </c>
       <c r="B28" t="n">
         <v>78543</v>
@@ -3453,13 +3453,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>376410</v>
+        <v>376511</v>
       </c>
       <c r="R28" t="n">
-        <v>6928948</v>
+        <v>6928908</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3515,10 +3515,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120462911</v>
+        <v>120462872</v>
       </c>
       <c r="B29" t="n">
-        <v>90580</v>
+        <v>78543</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3531,37 +3531,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>230405</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>376433</v>
+        <v>376420</v>
       </c>
       <c r="R29" t="n">
-        <v>6928842</v>
+        <v>6928868</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3605,19 +3605,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120464178</v>
+        <v>120462219</v>
       </c>
       <c r="B30" t="n">
         <v>78542</v>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>376767</v>
+        <v>376700</v>
       </c>
       <c r="R30" t="n">
-        <v>6928875</v>
+        <v>6928752</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3719,7 +3719,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120464351</v>
+        <v>120461861</v>
       </c>
       <c r="B31" t="n">
         <v>74654</v>
@@ -3759,10 +3759,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>376822</v>
+        <v>376772</v>
       </c>
       <c r="R31" t="n">
-        <v>6928965</v>
+        <v>6928732</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3821,7 +3821,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120461976</v>
+        <v>120462372</v>
       </c>
       <c r="B32" t="n">
         <v>78542</v>
@@ -3857,17 +3857,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>376741</v>
+        <v>376659</v>
       </c>
       <c r="R32" t="n">
-        <v>6928740</v>
+        <v>6928762</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3911,19 +3911,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120462766</v>
+        <v>120462917</v>
       </c>
       <c r="B33" t="n">
         <v>78542</v>
@@ -3963,13 +3963,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>376533</v>
+        <v>376403</v>
       </c>
       <c r="R33" t="n">
-        <v>6928800</v>
+        <v>6928904</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4013,22 +4013,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120463768</v>
+        <v>120463131</v>
       </c>
       <c r="B34" t="n">
-        <v>78542</v>
+        <v>78543</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4041,16 +4041,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4065,10 +4065,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>376653</v>
+        <v>376470</v>
       </c>
       <c r="R34" t="n">
-        <v>6928851</v>
+        <v>6928960</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4127,10 +4127,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120462573</v>
+        <v>120464218</v>
       </c>
       <c r="B35" t="n">
-        <v>74654</v>
+        <v>90580</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4143,21 +4143,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4167,10 +4167,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>376605</v>
+        <v>376778</v>
       </c>
       <c r="R35" t="n">
-        <v>6928771</v>
+        <v>6928905</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4229,7 +4229,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120461902</v>
+        <v>120463133</v>
       </c>
       <c r="B36" t="n">
         <v>78542</v>
@@ -4265,17 +4265,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>376797</v>
+        <v>376426</v>
       </c>
       <c r="R36" t="n">
-        <v>6928746</v>
+        <v>6928956</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4319,22 +4319,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120462796</v>
+        <v>120462783</v>
       </c>
       <c r="B37" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4347,37 +4347,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>376500</v>
+        <v>376448</v>
       </c>
       <c r="R37" t="n">
-        <v>6928798</v>
+        <v>6928821</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4421,22 +4421,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120464085</v>
+        <v>120462799</v>
       </c>
       <c r="B38" t="n">
-        <v>78542</v>
+        <v>78543</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4449,16 +4449,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>376731</v>
+        <v>376432</v>
       </c>
       <c r="R38" t="n">
-        <v>6928890</v>
+        <v>6928842</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4523,22 +4523,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120461838</v>
+        <v>120463172</v>
       </c>
       <c r="B39" t="n">
-        <v>79624</v>
+        <v>90864</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4551,37 +4551,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>376813</v>
+        <v>376427</v>
       </c>
       <c r="R39" t="n">
-        <v>6928747</v>
+        <v>6928969</v>
       </c>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4625,22 +4625,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120464110</v>
+        <v>120461491</v>
       </c>
       <c r="B40" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4653,21 +4653,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4677,10 +4677,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>376748</v>
+        <v>376797</v>
       </c>
       <c r="R40" t="n">
-        <v>6928890</v>
+        <v>6928714</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4739,10 +4739,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120463009</v>
+        <v>120462877</v>
       </c>
       <c r="B41" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4755,34 +4755,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>376424</v>
+        <v>376442</v>
       </c>
       <c r="R41" t="n">
-        <v>6928913</v>
+        <v>6928809</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4841,10 +4841,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120463679</v>
+        <v>120461838</v>
       </c>
       <c r="B42" t="n">
-        <v>90598</v>
+        <v>79624</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4857,34 +4857,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>376629</v>
+        <v>376813</v>
       </c>
       <c r="R42" t="n">
-        <v>6928862</v>
+        <v>6928747</v>
       </c>
       <c r="S42" t="n">
         <v>3</v>
@@ -4943,10 +4943,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120463199</v>
+        <v>120463161</v>
       </c>
       <c r="B43" t="n">
-        <v>79624</v>
+        <v>78543</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4959,37 +4959,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>230405</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>376466</v>
+        <v>376500</v>
       </c>
       <c r="R43" t="n">
-        <v>6928935</v>
+        <v>6928936</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5033,22 +5033,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120462773</v>
+        <v>120464110</v>
       </c>
       <c r="B44" t="n">
-        <v>79624</v>
+        <v>90598</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5061,21 +5061,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5085,10 +5085,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>376533</v>
+        <v>376748</v>
       </c>
       <c r="R44" t="n">
-        <v>6928800</v>
+        <v>6928890</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5147,10 +5147,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120463089</v>
+        <v>120463199</v>
       </c>
       <c r="B45" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5163,34 +5163,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>376419</v>
+        <v>376466</v>
       </c>
       <c r="R45" t="n">
-        <v>6928951</v>
+        <v>6928935</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5249,10 +5249,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120463188</v>
+        <v>120462971</v>
       </c>
       <c r="B46" t="n">
-        <v>78542</v>
+        <v>78543</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5265,16 +5265,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5285,17 +5285,17 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>376452</v>
+        <v>376410</v>
       </c>
       <c r="R46" t="n">
-        <v>6928954</v>
+        <v>6928948</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5339,22 +5339,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120463458</v>
+        <v>120461902</v>
       </c>
       <c r="B47" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5367,37 +5367,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>376530</v>
+        <v>376797</v>
       </c>
       <c r="R47" t="n">
-        <v>6928871</v>
+        <v>6928746</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5441,22 +5441,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120464355</v>
+        <v>120461553</v>
       </c>
       <c r="B48" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5469,21 +5469,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5493,10 +5493,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>376822</v>
+        <v>376797</v>
       </c>
       <c r="R48" t="n">
-        <v>6928965</v>
+        <v>6928714</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5555,10 +5555,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120463433</v>
+        <v>120464210</v>
       </c>
       <c r="B49" t="n">
-        <v>78543</v>
+        <v>78542</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5571,16 +5571,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5591,17 +5591,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>376511</v>
+        <v>376763</v>
       </c>
       <c r="R49" t="n">
-        <v>6928908</v>
+        <v>6928949</v>
       </c>
       <c r="S49" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120464210</v>
+        <v>120463089</v>
       </c>
       <c r="B50" t="n">
         <v>78542</v>
@@ -5693,17 +5693,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>376763</v>
+        <v>376419</v>
       </c>
       <c r="R50" t="n">
-        <v>6928949</v>
+        <v>6928951</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5747,22 +5747,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120461419</v>
+        <v>120463768</v>
       </c>
       <c r="B51" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5775,34 +5775,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>376841</v>
+        <v>376653</v>
       </c>
       <c r="R51" t="n">
-        <v>6928719</v>
+        <v>6928851</v>
       </c>
       <c r="S51" t="n">
         <v>4</v>
@@ -5861,10 +5861,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120463650</v>
+        <v>120463914</v>
       </c>
       <c r="B52" t="n">
-        <v>78641</v>
+        <v>90576</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5877,21 +5877,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>967</v>
+        <v>1108</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>376627</v>
+        <v>376684</v>
       </c>
       <c r="R52" t="n">
-        <v>6928864</v>
+        <v>6928823</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5963,10 +5963,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120461440</v>
+        <v>120461918</v>
       </c>
       <c r="B53" t="n">
-        <v>79659</v>
+        <v>74654</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5975,25 +5975,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6003,10 +6003,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>376797</v>
+        <v>376774</v>
       </c>
       <c r="R53" t="n">
-        <v>6928714</v>
+        <v>6928741</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6065,10 +6065,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120464264</v>
+        <v>120463773</v>
       </c>
       <c r="B54" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6081,34 +6081,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>376784</v>
+        <v>376666</v>
       </c>
       <c r="R54" t="n">
-        <v>6928921</v>
+        <v>6928860</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6167,10 +6167,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120462219</v>
+        <v>120462709</v>
       </c>
       <c r="B55" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6183,21 +6183,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6207,10 +6207,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>376700</v>
+        <v>376574</v>
       </c>
       <c r="R55" t="n">
-        <v>6928752</v>
+        <v>6928783</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6269,10 +6269,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120464020</v>
+        <v>120463009</v>
       </c>
       <c r="B56" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6285,37 +6285,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>376688</v>
+        <v>376424</v>
       </c>
       <c r="R56" t="n">
-        <v>6928842</v>
+        <v>6928913</v>
       </c>
       <c r="S56" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6359,19 +6359,19 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120461491</v>
+        <v>120462634</v>
       </c>
       <c r="B57" t="n">
         <v>78542</v>
@@ -6411,10 +6411,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>376797</v>
+        <v>376605</v>
       </c>
       <c r="R57" t="n">
-        <v>6928714</v>
+        <v>6928771</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6575,10 +6575,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120464205</v>
+        <v>120464038</v>
       </c>
       <c r="B59" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6591,21 +6591,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>376778</v>
+        <v>376719</v>
       </c>
       <c r="R59" t="n">
-        <v>6928905</v>
+        <v>6928860</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6677,10 +6677,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120462634</v>
+        <v>120464020</v>
       </c>
       <c r="B60" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6693,37 +6693,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>376605</v>
+        <v>376688</v>
       </c>
       <c r="R60" t="n">
-        <v>6928771</v>
+        <v>6928842</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6767,22 +6767,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120462709</v>
+        <v>120462738</v>
       </c>
       <c r="B61" t="n">
-        <v>90598</v>
+        <v>90594</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6795,21 +6795,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6819,10 +6819,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>376574</v>
+        <v>376546</v>
       </c>
       <c r="R61" t="n">
-        <v>6928783</v>
+        <v>6928799</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6881,10 +6881,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120463914</v>
+        <v>120461364</v>
       </c>
       <c r="B62" t="n">
-        <v>90576</v>
+        <v>90580</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6897,34 +6897,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>376684</v>
+        <v>376857</v>
       </c>
       <c r="R62" t="n">
-        <v>6928823</v>
+        <v>6928677</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6983,10 +6983,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120461553</v>
+        <v>120464264</v>
       </c>
       <c r="B63" t="n">
-        <v>79624</v>
+        <v>90580</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6999,21 +6999,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7023,10 +7023,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>376797</v>
+        <v>376784</v>
       </c>
       <c r="R63" t="n">
-        <v>6928714</v>
+        <v>6928921</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7085,7 +7085,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120461973</v>
+        <v>120463769</v>
       </c>
       <c r="B64" t="n">
         <v>74654</v>
@@ -7121,14 +7121,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>376741</v>
+        <v>376666</v>
       </c>
       <c r="R64" t="n">
-        <v>6928740</v>
+        <v>6928860</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7187,10 +7187,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120462344</v>
+        <v>120464111</v>
       </c>
       <c r="B65" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7203,37 +7203,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>376677</v>
+        <v>376700</v>
       </c>
       <c r="R65" t="n">
-        <v>6928749</v>
+        <v>6928867</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7277,22 +7277,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120463175</v>
+        <v>120462766</v>
       </c>
       <c r="B66" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7305,34 +7305,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>376427</v>
+        <v>376533</v>
       </c>
       <c r="R66" t="n">
-        <v>6928969</v>
+        <v>6928800</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7391,10 +7391,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120462738</v>
+        <v>120461976</v>
       </c>
       <c r="B67" t="n">
-        <v>90594</v>
+        <v>78542</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7407,21 +7407,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7431,10 +7431,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>376546</v>
+        <v>376741</v>
       </c>
       <c r="R67" t="n">
-        <v>6928799</v>
+        <v>6928740</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7493,10 +7493,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120463131</v>
+        <v>120461440</v>
       </c>
       <c r="B68" t="n">
-        <v>78543</v>
+        <v>79659</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7505,25 +7505,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>230405</v>
+        <v>6464</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7533,13 +7533,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>376470</v>
+        <v>376797</v>
       </c>
       <c r="R68" t="n">
-        <v>6928960</v>
+        <v>6928714</v>
       </c>
       <c r="S68" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7583,22 +7583,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120463161</v>
+        <v>120462911</v>
       </c>
       <c r="B69" t="n">
-        <v>78543</v>
+        <v>90580</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7611,37 +7611,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>230405</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>376500</v>
+        <v>376433</v>
       </c>
       <c r="R69" t="n">
-        <v>6928936</v>
+        <v>6928842</v>
       </c>
       <c r="S69" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7685,22 +7685,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120462799</v>
+        <v>120464205</v>
       </c>
       <c r="B70" t="n">
-        <v>78543</v>
+        <v>90598</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7713,21 +7713,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>230405</v>
+        <v>5432</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7737,13 +7737,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>376432</v>
+        <v>376778</v>
       </c>
       <c r="R70" t="n">
-        <v>6928842</v>
+        <v>6928905</v>
       </c>
       <c r="S70" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7787,19 +7787,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120461918</v>
+        <v>120461973</v>
       </c>
       <c r="B71" t="n">
         <v>74654</v>
@@ -7839,10 +7839,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>376774</v>
+        <v>376741</v>
       </c>
       <c r="R71" t="n">
-        <v>6928741</v>
+        <v>6928740</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7901,10 +7901,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120463773</v>
+        <v>120464351</v>
       </c>
       <c r="B72" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7917,34 +7917,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>376666</v>
+        <v>376822</v>
       </c>
       <c r="R72" t="n">
-        <v>6928860</v>
+        <v>6928965</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8003,10 +8003,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120462931</v>
+        <v>120463824</v>
       </c>
       <c r="B73" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8019,21 +8019,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>376436</v>
+        <v>376695</v>
       </c>
       <c r="R73" t="n">
-        <v>6928867</v>
+        <v>6928830</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8105,10 +8105,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120463512</v>
+        <v>120464178</v>
       </c>
       <c r="B74" t="n">
-        <v>78543</v>
+        <v>78542</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8121,16 +8121,16 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -8145,13 +8145,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>376585</v>
+        <v>376767</v>
       </c>
       <c r="R74" t="n">
-        <v>6928865</v>
+        <v>6928875</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8195,12 +8195,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>

--- a/artfynd/A 38064-2024 artfynd.xlsx
+++ b/artfynd/A 38064-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120315897</v>
+        <v>120315911</v>
       </c>
       <c r="B2" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -731,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>376875</v>
+        <v>376797</v>
       </c>
       <c r="R2" t="n">
-        <v>6928715</v>
+        <v>6928695</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -771,7 +758,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Observerad under flera tillfällen under besöket</t>
+          <t>Flera platser i området</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -908,7 +896,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120315938</v>
+        <v>120315914</v>
       </c>
       <c r="B4" t="n">
         <v>57320</v>
@@ -956,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>376753</v>
+        <v>376706</v>
       </c>
       <c r="R4" t="n">
-        <v>6928863</v>
+        <v>6928747</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1018,7 +1006,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120315914</v>
+        <v>120315938</v>
       </c>
       <c r="B5" t="n">
         <v>57320</v>
@@ -1066,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>376706</v>
+        <v>376753</v>
       </c>
       <c r="R5" t="n">
-        <v>6928747</v>
+        <v>6928863</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,10 +1116,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120315928</v>
+        <v>120315897</v>
       </c>
       <c r="B6" t="n">
-        <v>78278</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,26 +1132,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1171,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>376678</v>
+        <v>376875</v>
       </c>
       <c r="R6" t="n">
-        <v>6928776</v>
+        <v>6928715</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,7 +1212,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Flera platser i området</t>
+          <t>Observerad under flera tillfällen under besöket</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,7 +1221,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1239,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120315911</v>
+        <v>120315928</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1255,21 +1255,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1282,10 +1282,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>376797</v>
+        <v>376678</v>
       </c>
       <c r="R7" t="n">
-        <v>6928695</v>
+        <v>6928776</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120462573</v>
+        <v>120463512</v>
       </c>
       <c r="B9" t="n">
-        <v>74654</v>
+        <v>78543</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1476,21 +1476,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>230405</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1500,13 +1500,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>376605</v>
+        <v>376585</v>
       </c>
       <c r="R9" t="n">
-        <v>6928771</v>
+        <v>6928865</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1550,19 +1550,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120464475</v>
+        <v>120464038</v>
       </c>
       <c r="B10" t="n">
         <v>78542</v>
@@ -1598,17 +1598,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>376903</v>
+        <v>376719</v>
       </c>
       <c r="R10" t="n">
-        <v>6928887</v>
+        <v>6928860</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1652,22 +1652,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120462344</v>
+        <v>120462884</v>
       </c>
       <c r="B11" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1680,21 +1680,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1704,13 +1704,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>376677</v>
+        <v>376415</v>
       </c>
       <c r="R11" t="n">
-        <v>6928749</v>
+        <v>6928886</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1754,22 +1754,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120463458</v>
+        <v>120462709</v>
       </c>
       <c r="B12" t="n">
-        <v>79624</v>
+        <v>90598</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1782,34 +1782,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>376530</v>
+        <v>376574</v>
       </c>
       <c r="R12" t="n">
-        <v>6928871</v>
+        <v>6928783</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1868,10 +1868,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120464397</v>
+        <v>120463650</v>
       </c>
       <c r="B13" t="n">
-        <v>56532</v>
+        <v>78641</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1880,56 +1880,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>967</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>övernattning</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>376843</v>
+        <v>376627</v>
       </c>
       <c r="R13" t="n">
-        <v>6928942</v>
+        <v>6928864</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1985,10 +1970,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120462884</v>
+        <v>120463914</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>90576</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2001,37 +1986,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>376415</v>
+        <v>376684</v>
       </c>
       <c r="R14" t="n">
-        <v>6928886</v>
+        <v>6928823</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2075,22 +2060,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120463650</v>
+        <v>120461382</v>
       </c>
       <c r="B15" t="n">
-        <v>78641</v>
+        <v>79624</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2103,34 +2088,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>967</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>376627</v>
+        <v>376842</v>
       </c>
       <c r="R15" t="n">
-        <v>6928864</v>
+        <v>6928689</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2189,10 +2174,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120462796</v>
+        <v>120461553</v>
       </c>
       <c r="B16" t="n">
-        <v>74654</v>
+        <v>79624</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2205,21 +2190,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2229,10 +2214,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>376500</v>
+        <v>376797</v>
       </c>
       <c r="R16" t="n">
-        <v>6928798</v>
+        <v>6928714</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2291,10 +2276,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120461419</v>
+        <v>120463679</v>
       </c>
       <c r="B17" t="n">
-        <v>79624</v>
+        <v>90598</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2307,37 +2292,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>376841</v>
+        <v>376629</v>
       </c>
       <c r="R17" t="n">
-        <v>6928719</v>
+        <v>6928862</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2393,10 +2378,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120462773</v>
+        <v>120462796</v>
       </c>
       <c r="B18" t="n">
-        <v>79624</v>
+        <v>74654</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2409,21 +2394,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2433,10 +2418,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>376533</v>
+        <v>376500</v>
       </c>
       <c r="R18" t="n">
-        <v>6928800</v>
+        <v>6928798</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2495,10 +2480,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120461382</v>
+        <v>120463161</v>
       </c>
       <c r="B19" t="n">
-        <v>79624</v>
+        <v>78543</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2511,21 +2496,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>230405</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2535,13 +2520,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>376842</v>
+        <v>376500</v>
       </c>
       <c r="R19" t="n">
-        <v>6928689</v>
+        <v>6928936</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2585,22 +2570,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120461377</v>
+        <v>120464218</v>
       </c>
       <c r="B20" t="n">
-        <v>79624</v>
+        <v>90580</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2613,37 +2598,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>376858</v>
+        <v>376778</v>
       </c>
       <c r="R20" t="n">
-        <v>6928712</v>
+        <v>6928905</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2687,22 +2672,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120463512</v>
+        <v>120464351</v>
       </c>
       <c r="B21" t="n">
-        <v>78543</v>
+        <v>74654</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2715,21 +2700,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>230405</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2739,13 +2724,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>376585</v>
+        <v>376822</v>
       </c>
       <c r="R21" t="n">
-        <v>6928865</v>
+        <v>6928965</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2789,22 +2774,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120464355</v>
+        <v>120463131</v>
       </c>
       <c r="B22" t="n">
-        <v>78542</v>
+        <v>78543</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2817,16 +2802,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2841,13 +2826,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>376822</v>
+        <v>376470</v>
       </c>
       <c r="R22" t="n">
-        <v>6928965</v>
+        <v>6928960</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2891,22 +2876,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120463188</v>
+        <v>120461973</v>
       </c>
       <c r="B23" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2919,34 +2904,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>376452</v>
+        <v>376741</v>
       </c>
       <c r="R23" t="n">
-        <v>6928954</v>
+        <v>6928740</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3005,10 +2990,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120463679</v>
+        <v>120462738</v>
       </c>
       <c r="B24" t="n">
-        <v>90598</v>
+        <v>90594</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3021,21 +3006,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3045,13 +3030,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>376629</v>
+        <v>376546</v>
       </c>
       <c r="R24" t="n">
-        <v>6928862</v>
+        <v>6928799</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3095,22 +3080,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120463175</v>
+        <v>120463824</v>
       </c>
       <c r="B25" t="n">
-        <v>90580</v>
+        <v>74654</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3123,34 +3108,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>376427</v>
+        <v>376695</v>
       </c>
       <c r="R25" t="n">
-        <v>6928969</v>
+        <v>6928830</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3209,10 +3194,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120464085</v>
+        <v>120464264</v>
       </c>
       <c r="B26" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3225,21 +3210,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3249,10 +3234,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>376731</v>
+        <v>376784</v>
       </c>
       <c r="R26" t="n">
-        <v>6928890</v>
+        <v>6928921</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3311,10 +3296,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120462931</v>
+        <v>120463172</v>
       </c>
       <c r="B27" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3327,34 +3312,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>376436</v>
+        <v>376427</v>
       </c>
       <c r="R27" t="n">
-        <v>6928867</v>
+        <v>6928969</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3413,10 +3398,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120463433</v>
+        <v>120464110</v>
       </c>
       <c r="B28" t="n">
-        <v>78543</v>
+        <v>90598</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3429,21 +3414,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>230405</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3453,13 +3438,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>376511</v>
+        <v>376748</v>
       </c>
       <c r="R28" t="n">
-        <v>6928908</v>
+        <v>6928890</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3503,22 +3488,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120462872</v>
+        <v>120462773</v>
       </c>
       <c r="B29" t="n">
-        <v>78543</v>
+        <v>79624</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3531,21 +3516,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>230405</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3555,13 +3540,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>376420</v>
+        <v>376533</v>
       </c>
       <c r="R29" t="n">
-        <v>6928868</v>
+        <v>6928800</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3605,22 +3590,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120462219</v>
+        <v>120463458</v>
       </c>
       <c r="B30" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3633,34 +3618,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>376700</v>
+        <v>376530</v>
       </c>
       <c r="R30" t="n">
-        <v>6928752</v>
+        <v>6928871</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3719,7 +3704,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120461861</v>
+        <v>120461918</v>
       </c>
       <c r="B31" t="n">
         <v>74654</v>
@@ -3759,10 +3744,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>376772</v>
+        <v>376774</v>
       </c>
       <c r="R31" t="n">
-        <v>6928732</v>
+        <v>6928741</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3821,7 +3806,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120462372</v>
+        <v>120463133</v>
       </c>
       <c r="B32" t="n">
         <v>78542</v>
@@ -3857,17 +3842,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>376659</v>
+        <v>376426</v>
       </c>
       <c r="R32" t="n">
-        <v>6928762</v>
+        <v>6928956</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3911,19 +3896,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120462917</v>
+        <v>120464475</v>
       </c>
       <c r="B33" t="n">
         <v>78542</v>
@@ -3959,17 +3944,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>376403</v>
+        <v>376903</v>
       </c>
       <c r="R33" t="n">
-        <v>6928904</v>
+        <v>6928887</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4025,10 +4010,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120463131</v>
+        <v>120462917</v>
       </c>
       <c r="B34" t="n">
-        <v>78543</v>
+        <v>78542</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4041,16 +4026,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4065,13 +4050,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>376470</v>
+        <v>376403</v>
       </c>
       <c r="R34" t="n">
-        <v>6928960</v>
+        <v>6928904</v>
       </c>
       <c r="S34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4127,10 +4112,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120464218</v>
+        <v>120461838</v>
       </c>
       <c r="B35" t="n">
-        <v>90580</v>
+        <v>79624</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4143,37 +4128,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>376778</v>
+        <v>376813</v>
       </c>
       <c r="R35" t="n">
-        <v>6928905</v>
+        <v>6928747</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4217,19 +4202,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120463133</v>
+        <v>120464111</v>
       </c>
       <c r="B36" t="n">
         <v>78542</v>
@@ -4265,17 +4250,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>376426</v>
+        <v>376700</v>
       </c>
       <c r="R36" t="n">
-        <v>6928956</v>
+        <v>6928867</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4319,22 +4304,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120462783</v>
+        <v>120462872</v>
       </c>
       <c r="B37" t="n">
-        <v>78542</v>
+        <v>78543</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4347,16 +4332,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4367,14 +4352,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>376448</v>
+        <v>376420</v>
       </c>
       <c r="R37" t="n">
-        <v>6928821</v>
+        <v>6928868</v>
       </c>
       <c r="S37" t="n">
         <v>3</v>
@@ -4433,10 +4418,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120462799</v>
+        <v>120463089</v>
       </c>
       <c r="B38" t="n">
-        <v>78543</v>
+        <v>78542</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4449,16 +4434,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4473,13 +4458,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>376432</v>
+        <v>376419</v>
       </c>
       <c r="R38" t="n">
-        <v>6928842</v>
+        <v>6928951</v>
       </c>
       <c r="S38" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4523,22 +4508,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120463172</v>
+        <v>120462344</v>
       </c>
       <c r="B39" t="n">
-        <v>90864</v>
+        <v>90598</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4551,34 +4536,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>376427</v>
+        <v>376677</v>
       </c>
       <c r="R39" t="n">
-        <v>6928969</v>
+        <v>6928749</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4637,10 +4622,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120461491</v>
+        <v>120463175</v>
       </c>
       <c r="B40" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4653,34 +4638,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>376797</v>
+        <v>376427</v>
       </c>
       <c r="R40" t="n">
-        <v>6928714</v>
+        <v>6928969</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4739,10 +4724,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120462877</v>
+        <v>120462971</v>
       </c>
       <c r="B41" t="n">
-        <v>74654</v>
+        <v>78543</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4755,37 +4740,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6440</v>
+        <v>230405</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>376442</v>
+        <v>376410</v>
       </c>
       <c r="R41" t="n">
-        <v>6928809</v>
+        <v>6928948</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4829,22 +4814,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120461838</v>
+        <v>120463433</v>
       </c>
       <c r="B42" t="n">
-        <v>79624</v>
+        <v>78543</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4857,34 +4842,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>230405</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>376813</v>
+        <v>376511</v>
       </c>
       <c r="R42" t="n">
-        <v>6928747</v>
+        <v>6928908</v>
       </c>
       <c r="S42" t="n">
         <v>3</v>
@@ -4943,10 +4928,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120463161</v>
+        <v>120462766</v>
       </c>
       <c r="B43" t="n">
-        <v>78543</v>
+        <v>78542</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4959,16 +4944,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4983,13 +4968,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>376500</v>
+        <v>376533</v>
       </c>
       <c r="R43" t="n">
-        <v>6928936</v>
+        <v>6928800</v>
       </c>
       <c r="S43" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5033,22 +5018,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120464110</v>
+        <v>120462219</v>
       </c>
       <c r="B44" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5061,21 +5046,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5085,10 +5070,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>376748</v>
+        <v>376700</v>
       </c>
       <c r="R44" t="n">
-        <v>6928890</v>
+        <v>6928752</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5147,10 +5132,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120463199</v>
+        <v>120463773</v>
       </c>
       <c r="B45" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5163,21 +5148,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5187,10 +5172,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>376466</v>
+        <v>376666</v>
       </c>
       <c r="R45" t="n">
-        <v>6928935</v>
+        <v>6928860</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5249,10 +5234,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120462971</v>
+        <v>120461861</v>
       </c>
       <c r="B46" t="n">
-        <v>78543</v>
+        <v>74654</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5265,21 +5250,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>230405</v>
+        <v>6440</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5289,13 +5274,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>376410</v>
+        <v>376772</v>
       </c>
       <c r="R46" t="n">
-        <v>6928948</v>
+        <v>6928732</v>
       </c>
       <c r="S46" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5339,22 +5324,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120461902</v>
+        <v>120464020</v>
       </c>
       <c r="B47" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5367,21 +5352,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5391,10 +5376,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>376797</v>
+        <v>376688</v>
       </c>
       <c r="R47" t="n">
-        <v>6928746</v>
+        <v>6928842</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -5453,10 +5438,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120461553</v>
+        <v>120463009</v>
       </c>
       <c r="B48" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5469,21 +5454,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5493,10 +5478,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>376797</v>
+        <v>376424</v>
       </c>
       <c r="R48" t="n">
-        <v>6928714</v>
+        <v>6928913</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5555,7 +5540,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120464210</v>
+        <v>120462372</v>
       </c>
       <c r="B49" t="n">
         <v>78542</v>
@@ -5595,13 +5580,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>376763</v>
+        <v>376659</v>
       </c>
       <c r="R49" t="n">
-        <v>6928949</v>
+        <v>6928762</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5657,7 +5642,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120463089</v>
+        <v>120461491</v>
       </c>
       <c r="B50" t="n">
         <v>78542</v>
@@ -5697,10 +5682,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>376419</v>
+        <v>376797</v>
       </c>
       <c r="R50" t="n">
-        <v>6928951</v>
+        <v>6928714</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5759,7 +5744,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120463768</v>
+        <v>120464355</v>
       </c>
       <c r="B51" t="n">
         <v>78542</v>
@@ -5799,13 +5784,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>376653</v>
+        <v>376822</v>
       </c>
       <c r="R51" t="n">
-        <v>6928851</v>
+        <v>6928965</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5849,22 +5834,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120463914</v>
+        <v>120461976</v>
       </c>
       <c r="B52" t="n">
-        <v>90576</v>
+        <v>78542</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5877,34 +5862,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>376684</v>
+        <v>376741</v>
       </c>
       <c r="R52" t="n">
-        <v>6928823</v>
+        <v>6928740</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5963,10 +5948,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120461918</v>
+        <v>120461440</v>
       </c>
       <c r="B53" t="n">
-        <v>74654</v>
+        <v>79659</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5975,25 +5960,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6003,10 +5988,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>376774</v>
+        <v>376797</v>
       </c>
       <c r="R53" t="n">
-        <v>6928741</v>
+        <v>6928714</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6065,7 +6050,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120463773</v>
+        <v>120462634</v>
       </c>
       <c r="B54" t="n">
         <v>78542</v>
@@ -6101,14 +6086,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>376666</v>
+        <v>376605</v>
       </c>
       <c r="R54" t="n">
-        <v>6928860</v>
+        <v>6928771</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6167,10 +6152,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120462709</v>
+        <v>120462911</v>
       </c>
       <c r="B55" t="n">
-        <v>90598</v>
+        <v>90580</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6183,34 +6168,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>376574</v>
+        <v>376433</v>
       </c>
       <c r="R55" t="n">
-        <v>6928783</v>
+        <v>6928842</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6269,10 +6254,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120463009</v>
+        <v>120462877</v>
       </c>
       <c r="B56" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6285,34 +6270,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>376424</v>
+        <v>376442</v>
       </c>
       <c r="R56" t="n">
-        <v>6928913</v>
+        <v>6928809</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6371,10 +6356,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120462634</v>
+        <v>120463199</v>
       </c>
       <c r="B57" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6387,34 +6372,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>376605</v>
+        <v>376466</v>
       </c>
       <c r="R57" t="n">
-        <v>6928771</v>
+        <v>6928935</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6473,7 +6458,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120464383</v>
+        <v>120461902</v>
       </c>
       <c r="B58" t="n">
         <v>78542</v>
@@ -6513,13 +6498,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>376836</v>
+        <v>376797</v>
       </c>
       <c r="R58" t="n">
-        <v>6928949</v>
+        <v>6928746</v>
       </c>
       <c r="S58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6575,7 +6560,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120464038</v>
+        <v>120464210</v>
       </c>
       <c r="B59" t="n">
         <v>78542</v>
@@ -6611,17 +6596,17 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>376719</v>
+        <v>376763</v>
       </c>
       <c r="R59" t="n">
-        <v>6928860</v>
+        <v>6928949</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6665,22 +6650,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120464020</v>
+        <v>120461364</v>
       </c>
       <c r="B60" t="n">
-        <v>79624</v>
+        <v>90580</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6693,37 +6678,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>376688</v>
+        <v>376857</v>
       </c>
       <c r="R60" t="n">
-        <v>6928842</v>
+        <v>6928677</v>
       </c>
       <c r="S60" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6767,22 +6752,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120462738</v>
+        <v>120463769</v>
       </c>
       <c r="B61" t="n">
-        <v>90594</v>
+        <v>74654</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6795,34 +6780,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1204</v>
+        <v>6440</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>376546</v>
+        <v>376666</v>
       </c>
       <c r="R61" t="n">
-        <v>6928799</v>
+        <v>6928860</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6881,10 +6866,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120461364</v>
+        <v>120463188</v>
       </c>
       <c r="B62" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6897,34 +6882,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>376857</v>
+        <v>376452</v>
       </c>
       <c r="R62" t="n">
-        <v>6928677</v>
+        <v>6928954</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6983,10 +6968,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120464264</v>
+        <v>120464178</v>
       </c>
       <c r="B63" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6999,21 +6984,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7023,10 +7008,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>376784</v>
+        <v>376767</v>
       </c>
       <c r="R63" t="n">
-        <v>6928921</v>
+        <v>6928875</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7085,10 +7070,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120463769</v>
+        <v>120464397</v>
       </c>
       <c r="B64" t="n">
-        <v>74654</v>
+        <v>56532</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7097,41 +7082,56 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6440</v>
+        <v>100138</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>övernattning</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>376666</v>
+        <v>376843</v>
       </c>
       <c r="R64" t="n">
-        <v>6928860</v>
+        <v>6928942</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120464111</v>
+        <v>120462931</v>
       </c>
       <c r="B65" t="n">
         <v>78542</v>
@@ -7223,17 +7223,17 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>376700</v>
+        <v>376436</v>
       </c>
       <c r="R65" t="n">
         <v>6928867</v>
       </c>
       <c r="S65" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7277,19 +7277,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120462766</v>
+        <v>120463768</v>
       </c>
       <c r="B66" t="n">
         <v>78542</v>
@@ -7329,13 +7329,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>376533</v>
+        <v>376653</v>
       </c>
       <c r="R66" t="n">
-        <v>6928800</v>
+        <v>6928851</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7379,19 +7379,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120461976</v>
+        <v>120464383</v>
       </c>
       <c r="B67" t="n">
         <v>78542</v>
@@ -7427,17 +7427,17 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>376741</v>
+        <v>376836</v>
       </c>
       <c r="R67" t="n">
-        <v>6928740</v>
+        <v>6928949</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7481,22 +7481,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120461440</v>
+        <v>120464085</v>
       </c>
       <c r="B68" t="n">
-        <v>79659</v>
+        <v>78542</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7505,25 +7505,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7533,10 +7533,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>376797</v>
+        <v>376731</v>
       </c>
       <c r="R68" t="n">
-        <v>6928714</v>
+        <v>6928890</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7595,10 +7595,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120462911</v>
+        <v>120462783</v>
       </c>
       <c r="B69" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7611,37 +7611,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>376433</v>
+        <v>376448</v>
       </c>
       <c r="R69" t="n">
-        <v>6928842</v>
+        <v>6928821</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7685,22 +7685,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120464205</v>
+        <v>120462799</v>
       </c>
       <c r="B70" t="n">
-        <v>90598</v>
+        <v>78543</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7713,21 +7713,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5432</v>
+        <v>230405</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7737,13 +7737,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>376778</v>
+        <v>376432</v>
       </c>
       <c r="R70" t="n">
-        <v>6928905</v>
+        <v>6928842</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7787,22 +7787,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120461973</v>
+        <v>120461419</v>
       </c>
       <c r="B71" t="n">
-        <v>74654</v>
+        <v>79624</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7815,37 +7815,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>376741</v>
+        <v>376841</v>
       </c>
       <c r="R71" t="n">
-        <v>6928740</v>
+        <v>6928719</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7889,19 +7889,19 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120464351</v>
+        <v>120462573</v>
       </c>
       <c r="B72" t="n">
         <v>74654</v>
@@ -7941,10 +7941,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>376822</v>
+        <v>376605</v>
       </c>
       <c r="R72" t="n">
-        <v>6928965</v>
+        <v>6928771</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8003,10 +8003,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120463824</v>
+        <v>120461377</v>
       </c>
       <c r="B73" t="n">
-        <v>74654</v>
+        <v>79624</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8019,37 +8019,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>376695</v>
+        <v>376858</v>
       </c>
       <c r="R73" t="n">
-        <v>6928830</v>
+        <v>6928712</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8093,22 +8093,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120464178</v>
+        <v>120464205</v>
       </c>
       <c r="B74" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8121,21 +8121,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8145,10 +8145,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>376767</v>
+        <v>376778</v>
       </c>
       <c r="R74" t="n">
-        <v>6928875</v>
+        <v>6928905</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>

--- a/artfynd/A 38064-2024 artfynd.xlsx
+++ b/artfynd/A 38064-2024 artfynd.xlsx
@@ -1562,10 +1562,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120464038</v>
+        <v>120463650</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>78641</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1578,34 +1578,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>376719</v>
+        <v>376627</v>
       </c>
       <c r="R10" t="n">
-        <v>6928860</v>
+        <v>6928864</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1664,10 +1664,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120462884</v>
+        <v>120463914</v>
       </c>
       <c r="B11" t="n">
-        <v>78542</v>
+        <v>90576</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1680,37 +1680,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>376415</v>
+        <v>376684</v>
       </c>
       <c r="R11" t="n">
-        <v>6928886</v>
+        <v>6928823</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1754,22 +1754,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120462709</v>
+        <v>120461382</v>
       </c>
       <c r="B12" t="n">
-        <v>90598</v>
+        <v>79624</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1782,21 +1782,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1806,10 +1806,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>376574</v>
+        <v>376842</v>
       </c>
       <c r="R12" t="n">
-        <v>6928783</v>
+        <v>6928689</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1868,10 +1868,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120463650</v>
+        <v>120461553</v>
       </c>
       <c r="B13" t="n">
-        <v>78641</v>
+        <v>79624</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1884,34 +1884,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>967</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>376627</v>
+        <v>376797</v>
       </c>
       <c r="R13" t="n">
-        <v>6928864</v>
+        <v>6928714</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1970,10 +1970,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120463914</v>
+        <v>120462709</v>
       </c>
       <c r="B14" t="n">
-        <v>90576</v>
+        <v>90598</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1986,34 +1986,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>376684</v>
+        <v>376574</v>
       </c>
       <c r="R14" t="n">
-        <v>6928823</v>
+        <v>6928783</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2072,10 +2072,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120461382</v>
+        <v>120464038</v>
       </c>
       <c r="B15" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2088,21 +2088,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2112,10 +2112,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>376842</v>
+        <v>376719</v>
       </c>
       <c r="R15" t="n">
-        <v>6928689</v>
+        <v>6928860</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2174,10 +2174,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120461553</v>
+        <v>120462884</v>
       </c>
       <c r="B16" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2190,21 +2190,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2214,13 +2214,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>376797</v>
+        <v>376415</v>
       </c>
       <c r="R16" t="n">
-        <v>6928714</v>
+        <v>6928886</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2264,12 +2264,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -3296,10 +3296,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120463172</v>
+        <v>120462773</v>
       </c>
       <c r="B27" t="n">
-        <v>90864</v>
+        <v>79624</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3312,34 +3312,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>376427</v>
+        <v>376533</v>
       </c>
       <c r="R27" t="n">
-        <v>6928969</v>
+        <v>6928800</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3398,10 +3398,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120464110</v>
+        <v>120463458</v>
       </c>
       <c r="B28" t="n">
-        <v>90598</v>
+        <v>79624</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3414,34 +3414,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>376748</v>
+        <v>376530</v>
       </c>
       <c r="R28" t="n">
-        <v>6928890</v>
+        <v>6928871</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3500,10 +3500,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120462773</v>
+        <v>120463172</v>
       </c>
       <c r="B29" t="n">
-        <v>79624</v>
+        <v>90864</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3516,34 +3516,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>376533</v>
+        <v>376427</v>
       </c>
       <c r="R29" t="n">
-        <v>6928800</v>
+        <v>6928969</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3602,10 +3602,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120463458</v>
+        <v>120464110</v>
       </c>
       <c r="B30" t="n">
-        <v>79624</v>
+        <v>90598</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3618,34 +3618,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>376530</v>
+        <v>376748</v>
       </c>
       <c r="R30" t="n">
-        <v>6928871</v>
+        <v>6928890</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -6152,10 +6152,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120462911</v>
+        <v>120462877</v>
       </c>
       <c r="B55" t="n">
-        <v>90580</v>
+        <v>74654</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6168,21 +6168,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6192,10 +6192,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>376433</v>
+        <v>376442</v>
       </c>
       <c r="R55" t="n">
-        <v>6928842</v>
+        <v>6928809</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6254,10 +6254,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120462877</v>
+        <v>120462911</v>
       </c>
       <c r="B56" t="n">
-        <v>74654</v>
+        <v>90580</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6270,21 +6270,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6294,10 +6294,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>376442</v>
+        <v>376433</v>
       </c>
       <c r="R56" t="n">
-        <v>6928809</v>
+        <v>6928842</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>

--- a/artfynd/A 38064-2024 artfynd.xlsx
+++ b/artfynd/A 38064-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120315903</v>
+        <v>120463172</v>
       </c>
       <c r="B2" t="n">
-        <v>57333</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 38064-2024, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>376869</v>
+        <v>376427</v>
       </c>
       <c r="R2" t="n">
-        <v>6928711</v>
+        <v>6928969</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120315914</v>
+        <v>120463650</v>
       </c>
       <c r="B3" t="n">
-        <v>57333</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,42 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>967</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 38064-2024, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>376706</v>
+        <v>376627</v>
       </c>
       <c r="R3" t="n">
-        <v>6928747</v>
+        <v>6928864</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -863,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,27 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120315910</v>
+        <v>120463914</v>
       </c>
       <c r="B4" t="n">
-        <v>57333</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -911,42 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 38064-2024, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>376797</v>
+        <v>376684</v>
       </c>
       <c r="R4" t="n">
-        <v>6928695</v>
+        <v>6928823</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,27 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120315938</v>
+        <v>120461364</v>
       </c>
       <c r="B5" t="n">
-        <v>57333</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,42 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 38064-2024, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>376753</v>
+        <v>376857</v>
       </c>
       <c r="R5" t="n">
-        <v>6928863</v>
+        <v>6928677</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,27 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120315897</v>
+        <v>120462911</v>
       </c>
       <c r="B6" t="n">
-        <v>57333</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1131,50 +1074,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 38064-2024, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>376875</v>
+        <v>376433</v>
       </c>
       <c r="R6" t="n">
-        <v>6928715</v>
+        <v>6928842</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,17 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Observerad under flera tillfällen under besöket</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,27 +1148,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120315911</v>
+        <v>120463175</v>
       </c>
       <c r="B7" t="n">
-        <v>78562</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1254,37 +1171,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 38064-2024, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>376797</v>
+        <v>376427</v>
       </c>
       <c r="R7" t="n">
-        <v>6928695</v>
+        <v>6928969</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,17 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Flera platser i området</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1330,34 +1239,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120315928</v>
+        <v>120464218</v>
       </c>
       <c r="B8" t="n">
-        <v>78298</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1365,37 +1268,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 38064-2024, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>376678</v>
+        <v>376778</v>
       </c>
       <c r="R8" t="n">
-        <v>6928776</v>
+        <v>6928905</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,17 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Flera platser i området</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,34 +1336,28 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120463089</v>
+        <v>120464264</v>
       </c>
       <c r="B9" t="n">
-        <v>78590</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1500,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>376419</v>
+        <v>376784</v>
       </c>
       <c r="R9" t="n">
-        <v>6928951</v>
+        <v>6928921</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,53 +1451,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120464210</v>
+        <v>120462738</v>
       </c>
       <c r="B10" t="n">
-        <v>78590</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>376763</v>
+        <v>376546</v>
       </c>
       <c r="R10" t="n">
-        <v>6928949</v>
+        <v>6928799</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1652,27 +1536,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120462219</v>
+        <v>120461377</v>
       </c>
       <c r="B11" t="n">
-        <v>78590</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1680,37 +1559,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>376700</v>
+        <v>376858</v>
       </c>
       <c r="R11" t="n">
-        <v>6928752</v>
+        <v>6928712</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1754,27 +1633,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120463175</v>
+        <v>120461382</v>
       </c>
       <c r="B12" t="n">
-        <v>90670</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1782,34 +1656,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>376427</v>
+        <v>376842</v>
       </c>
       <c r="R12" t="n">
-        <v>6928969</v>
+        <v>6928689</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1868,15 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120464218</v>
+        <v>120461419</v>
       </c>
       <c r="B13" t="n">
-        <v>90670</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1884,37 +1753,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>376778</v>
+        <v>376841</v>
       </c>
       <c r="R13" t="n">
-        <v>6928905</v>
+        <v>6928719</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1958,80 +1827,60 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120464397</v>
+        <v>120461553</v>
       </c>
       <c r="B14" t="n">
-        <v>56556</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>övernattning</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>376843</v>
+        <v>376797</v>
       </c>
       <c r="R14" t="n">
-        <v>6928942</v>
+        <v>6928714</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2087,15 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120464020</v>
+        <v>120461838</v>
       </c>
       <c r="B15" t="n">
-        <v>79672</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2127,13 +1971,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>376688</v>
+        <v>376813</v>
       </c>
       <c r="R15" t="n">
-        <v>6928842</v>
+        <v>6928747</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2189,15 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120462573</v>
+        <v>120462773</v>
       </c>
       <c r="B16" t="n">
-        <v>74698</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2205,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2229,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>376605</v>
+        <v>376533</v>
       </c>
       <c r="R16" t="n">
-        <v>6928771</v>
+        <v>6928800</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2291,15 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120463131</v>
+        <v>120463199</v>
       </c>
       <c r="B17" t="n">
-        <v>78591</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2307,37 +2141,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>230405</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>376470</v>
+        <v>376466</v>
       </c>
       <c r="R17" t="n">
-        <v>6928960</v>
+        <v>6928935</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2381,27 +2215,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120462799</v>
+        <v>120463458</v>
       </c>
       <c r="B18" t="n">
-        <v>78591</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2409,37 +2238,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>230405</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>376432</v>
+        <v>376530</v>
       </c>
       <c r="R18" t="n">
-        <v>6928842</v>
+        <v>6928871</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2483,27 +2312,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120463679</v>
+        <v>120464020</v>
       </c>
       <c r="B19" t="n">
-        <v>90688</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2511,37 +2335,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>376629</v>
+        <v>376688</v>
       </c>
       <c r="R19" t="n">
-        <v>6928862</v>
+        <v>6928842</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2597,50 +2421,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120464205</v>
+        <v>120315911</v>
       </c>
       <c r="B20" t="n">
-        <v>90688</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>A 38064-2024, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>376778</v>
+        <v>376797</v>
       </c>
       <c r="R20" t="n">
-        <v>6928905</v>
+        <v>6928695</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2667,12 +2489,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Flera platser i området</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2681,37 +2508,33 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120464178</v>
+        <v>120459553</v>
       </c>
       <c r="B21" t="n">
-        <v>78590</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2739,10 +2562,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>376767</v>
+        <v>376934</v>
       </c>
       <c r="R21" t="n">
-        <v>6928875</v>
+        <v>6928841</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2801,19 +2624,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120461902</v>
+        <v>120459601</v>
       </c>
       <c r="B22" t="n">
-        <v>78590</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2841,10 +2659,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>376797</v>
+        <v>376916</v>
       </c>
       <c r="R22" t="n">
-        <v>6928746</v>
+        <v>6928831</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -2903,19 +2721,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120463773</v>
+        <v>120461491</v>
       </c>
       <c r="B23" t="n">
-        <v>78590</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2939,14 +2752,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>376666</v>
+        <v>376797</v>
       </c>
       <c r="R23" t="n">
-        <v>6928860</v>
+        <v>6928714</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3005,19 +2818,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120463188</v>
+        <v>120461902</v>
       </c>
       <c r="B24" t="n">
-        <v>78590</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3041,17 +2849,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>376452</v>
+        <v>376797</v>
       </c>
       <c r="R24" t="n">
-        <v>6928954</v>
+        <v>6928746</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3095,49 +2903,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120461973</v>
+        <v>120461976</v>
       </c>
       <c r="B25" t="n">
-        <v>74698</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3209,19 +3012,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120463133</v>
+        <v>120462219</v>
       </c>
       <c r="B26" t="n">
-        <v>78590</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3249,10 +3047,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>376426</v>
+        <v>376700</v>
       </c>
       <c r="R26" t="n">
-        <v>6928956</v>
+        <v>6928752</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3311,19 +3109,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120462884</v>
+        <v>120462372</v>
       </c>
       <c r="B27" t="n">
-        <v>78590</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3347,14 +3140,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>376415</v>
+        <v>376659</v>
       </c>
       <c r="R27" t="n">
-        <v>6928886</v>
+        <v>6928762</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3413,50 +3206,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120463914</v>
+        <v>120462634</v>
       </c>
       <c r="B28" t="n">
-        <v>90666</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>376684</v>
+        <v>376605</v>
       </c>
       <c r="R28" t="n">
-        <v>6928823</v>
+        <v>6928771</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3515,53 +3303,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120461377</v>
+        <v>120462766</v>
       </c>
       <c r="B29" t="n">
-        <v>79672</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>376858</v>
+        <v>376533</v>
       </c>
       <c r="R29" t="n">
-        <v>6928712</v>
+        <v>6928800</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3605,31 +3388,26 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120464038</v>
+        <v>120462783</v>
       </c>
       <c r="B30" t="n">
-        <v>78590</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3653,17 +3431,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>376719</v>
+        <v>376448</v>
       </c>
       <c r="R30" t="n">
-        <v>6928860</v>
+        <v>6928821</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3707,31 +3485,26 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120462783</v>
+        <v>120462884</v>
       </c>
       <c r="B31" t="n">
-        <v>78590</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -3755,17 +3528,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>376448</v>
+        <v>376415</v>
       </c>
       <c r="R31" t="n">
-        <v>6928821</v>
+        <v>6928886</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3824,16 +3597,11 @@
         <v>120462917</v>
       </c>
       <c r="B32" t="n">
-        <v>78590</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -3923,19 +3691,14 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120464085</v>
+        <v>120462931</v>
       </c>
       <c r="B33" t="n">
-        <v>78590</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -3963,10 +3726,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>376731</v>
+        <v>376436</v>
       </c>
       <c r="R33" t="n">
-        <v>6928890</v>
+        <v>6928867</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4025,50 +3788,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120463650</v>
+        <v>120463009</v>
       </c>
       <c r="B34" t="n">
-        <v>78689</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>376627</v>
+        <v>376424</v>
       </c>
       <c r="R34" t="n">
-        <v>6928864</v>
+        <v>6928913</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4127,37 +3885,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120464264</v>
+        <v>120463089</v>
       </c>
       <c r="B35" t="n">
-        <v>90670</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4167,10 +3920,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>376784</v>
+        <v>376419</v>
       </c>
       <c r="R35" t="n">
-        <v>6928921</v>
+        <v>6928951</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4229,32 +3982,27 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120463433</v>
+        <v>120463133</v>
       </c>
       <c r="B36" t="n">
-        <v>78591</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4269,13 +4017,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>376511</v>
+        <v>376426</v>
       </c>
       <c r="R36" t="n">
-        <v>6928908</v>
+        <v>6928956</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4319,31 +4067,26 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120464383</v>
+        <v>120463188</v>
       </c>
       <c r="B37" t="n">
-        <v>78590</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4367,17 +4110,17 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>376836</v>
+        <v>376452</v>
       </c>
       <c r="R37" t="n">
-        <v>6928949</v>
+        <v>6928954</v>
       </c>
       <c r="S37" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4421,49 +4164,44 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120462796</v>
+        <v>120463768</v>
       </c>
       <c r="B38" t="n">
-        <v>74698</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4473,13 +4211,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>376500</v>
+        <v>376653</v>
       </c>
       <c r="R38" t="n">
-        <v>6928798</v>
+        <v>6928851</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4523,31 +4261,26 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120464111</v>
+        <v>120463773</v>
       </c>
       <c r="B39" t="n">
-        <v>78590</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -4571,17 +4304,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>376700</v>
+        <v>376666</v>
       </c>
       <c r="R39" t="n">
-        <v>6928867</v>
+        <v>6928860</v>
       </c>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4625,65 +4358,60 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120461419</v>
+        <v>120464038</v>
       </c>
       <c r="B40" t="n">
-        <v>79672</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>376841</v>
+        <v>376719</v>
       </c>
       <c r="R40" t="n">
-        <v>6928719</v>
+        <v>6928860</v>
       </c>
       <c r="S40" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4727,31 +4455,26 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120464355</v>
+        <v>120464085</v>
       </c>
       <c r="B41" t="n">
-        <v>78590</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -4779,10 +4502,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>376822</v>
+        <v>376731</v>
       </c>
       <c r="R41" t="n">
-        <v>6928965</v>
+        <v>6928890</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4841,19 +4564,14 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120461976</v>
+        <v>120464111</v>
       </c>
       <c r="B42" t="n">
-        <v>78590</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -4877,17 +4595,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>376741</v>
+        <v>376700</v>
       </c>
       <c r="R42" t="n">
-        <v>6928740</v>
+        <v>6928867</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4931,31 +4649,26 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120462372</v>
+        <v>120464178</v>
       </c>
       <c r="B43" t="n">
-        <v>78590</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -4979,17 +4692,17 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>376659</v>
+        <v>376767</v>
       </c>
       <c r="R43" t="n">
-        <v>6928762</v>
+        <v>6928875</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5033,49 +4746,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120461838</v>
+        <v>120464210</v>
       </c>
       <c r="B44" t="n">
-        <v>79672</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5085,13 +4793,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>376813</v>
+        <v>376763</v>
       </c>
       <c r="R44" t="n">
-        <v>6928747</v>
+        <v>6928949</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5147,50 +4855,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120463458</v>
+        <v>120464355</v>
       </c>
       <c r="B45" t="n">
-        <v>79672</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>376530</v>
+        <v>376822</v>
       </c>
       <c r="R45" t="n">
-        <v>6928871</v>
+        <v>6928965</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5249,19 +4952,14 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120462634</v>
+        <v>120464383</v>
       </c>
       <c r="B46" t="n">
-        <v>78590</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -5285,17 +4983,17 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>376605</v>
+        <v>376836</v>
       </c>
       <c r="R46" t="n">
-        <v>6928771</v>
+        <v>6928949</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5339,65 +5037,60 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120463824</v>
+        <v>120464475</v>
       </c>
       <c r="B47" t="n">
-        <v>74698</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>376695</v>
+        <v>376903</v>
       </c>
       <c r="R47" t="n">
-        <v>6928830</v>
+        <v>6928887</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5441,27 +5134,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120461364</v>
+        <v>120461333</v>
       </c>
       <c r="B48" t="n">
-        <v>90670</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5469,21 +5157,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>6437</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5493,10 +5181,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>376857</v>
+        <v>376873</v>
       </c>
       <c r="R48" t="n">
-        <v>6928677</v>
+        <v>6928654</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5555,15 +5243,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120463768</v>
+        <v>120461861</v>
       </c>
       <c r="B49" t="n">
-        <v>78590</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5571,21 +5254,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5595,13 +5278,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>376653</v>
+        <v>376772</v>
       </c>
       <c r="R49" t="n">
-        <v>6928851</v>
+        <v>6928732</v>
       </c>
       <c r="S49" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5645,27 +5328,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120463199</v>
+        <v>120461918</v>
       </c>
       <c r="B50" t="n">
-        <v>79672</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5673,34 +5351,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>376466</v>
+        <v>376774</v>
       </c>
       <c r="R50" t="n">
-        <v>6928935</v>
+        <v>6928741</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5759,15 +5437,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120463512</v>
+        <v>120461973</v>
       </c>
       <c r="B51" t="n">
-        <v>78591</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5775,21 +5448,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>230405</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5799,13 +5472,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>376585</v>
+        <v>376741</v>
       </c>
       <c r="R51" t="n">
-        <v>6928865</v>
+        <v>6928740</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5849,27 +5522,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120462911</v>
+        <v>120462573</v>
       </c>
       <c r="B52" t="n">
-        <v>90670</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5877,34 +5545,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>376433</v>
+        <v>376605</v>
       </c>
       <c r="R52" t="n">
-        <v>6928842</v>
+        <v>6928771</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5963,15 +5631,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120461861</v>
+        <v>120462796</v>
       </c>
       <c r="B53" t="n">
-        <v>74698</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6003,10 +5666,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>376772</v>
+        <v>376500</v>
       </c>
       <c r="R53" t="n">
-        <v>6928732</v>
+        <v>6928798</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6065,15 +5728,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120462709</v>
+        <v>120462877</v>
       </c>
       <c r="B54" t="n">
-        <v>90688</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6081,34 +5739,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>376574</v>
+        <v>376442</v>
       </c>
       <c r="R54" t="n">
-        <v>6928783</v>
+        <v>6928809</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6167,15 +5825,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120464475</v>
+        <v>120463769</v>
       </c>
       <c r="B55" t="n">
-        <v>78590</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6183,37 +5836,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Rödtjärnbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>376903</v>
+        <v>376666</v>
       </c>
       <c r="R55" t="n">
-        <v>6928887</v>
+        <v>6928860</v>
       </c>
       <c r="S55" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6257,27 +5910,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120462872</v>
+        <v>120463824</v>
       </c>
       <c r="B56" t="n">
-        <v>78591</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6285,21 +5933,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>230405</v>
+        <v>6440</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6309,13 +5957,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>376420</v>
+        <v>376695</v>
       </c>
       <c r="R56" t="n">
-        <v>6928868</v>
+        <v>6928830</v>
       </c>
       <c r="S56" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6359,27 +6007,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120462738</v>
+        <v>120464351</v>
       </c>
       <c r="B57" t="n">
-        <v>90684</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6387,21 +6030,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1204</v>
+        <v>6440</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6411,10 +6054,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>376546</v>
+        <v>376822</v>
       </c>
       <c r="R57" t="n">
-        <v>6928799</v>
+        <v>6928965</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6473,15 +6116,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120462766</v>
+        <v>120315928</v>
       </c>
       <c r="B58" t="n">
-        <v>78590</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6489,34 +6127,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>A 38064-2024, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>376533</v>
+        <v>376678</v>
       </c>
       <c r="R58" t="n">
-        <v>6928800</v>
+        <v>6928776</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6543,12 +6184,17 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Flera platser i området</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6557,18 +6203,19 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6578,12 +6225,7 @@
         <v>120461440</v>
       </c>
       <c r="B59" t="n">
-        <v>79707</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6677,15 +6319,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120463769</v>
+        <v>120461329</v>
       </c>
       <c r="B60" t="n">
-        <v>74698</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78334</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6693,34 +6330,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6440</v>
+        <v>6487</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>376666</v>
+        <v>376873</v>
       </c>
       <c r="R60" t="n">
-        <v>6928860</v>
+        <v>6928654</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6779,15 +6416,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120464351</v>
+        <v>120315897</v>
       </c>
       <c r="B61" t="n">
-        <v>74698</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6795,34 +6427,50 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>A 38064-2024, Hjd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>376822</v>
+        <v>376875</v>
       </c>
       <c r="R61" t="n">
-        <v>6928965</v>
+        <v>6928715</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6849,12 +6497,17 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Observerad under flera tillfällen under besöket</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6869,27 +6522,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120461491</v>
+        <v>120315903</v>
       </c>
       <c r="B62" t="n">
-        <v>78590</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6897,34 +6545,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>A 38064-2024, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>376797</v>
+        <v>376869</v>
       </c>
       <c r="R62" t="n">
-        <v>6928714</v>
+        <v>6928711</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6951,12 +6607,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6971,27 +6627,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120462971</v>
+        <v>120315910</v>
       </c>
       <c r="B63" t="n">
-        <v>78591</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6999,37 +6650,45 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>230405</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>A 38064-2024, Hjd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>376410</v>
+        <v>376797</v>
       </c>
       <c r="R63" t="n">
-        <v>6928948</v>
+        <v>6928695</v>
       </c>
       <c r="S63" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7053,12 +6712,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7073,27 +6732,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120463161</v>
+        <v>120315914</v>
       </c>
       <c r="B64" t="n">
-        <v>78591</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7101,37 +6755,45 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>230405</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>A 38064-2024, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>376500</v>
+        <v>376706</v>
       </c>
       <c r="R64" t="n">
-        <v>6928936</v>
+        <v>6928747</v>
       </c>
       <c r="S64" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7155,12 +6817,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7175,27 +6837,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120461382</v>
+        <v>120315938</v>
       </c>
       <c r="B65" t="n">
-        <v>79672</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7203,34 +6860,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>A 38064-2024, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>376842</v>
+        <v>376753</v>
       </c>
       <c r="R65" t="n">
-        <v>6928689</v>
+        <v>6928863</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7257,12 +6922,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7277,65 +6942,75 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120464110</v>
+        <v>120464397</v>
       </c>
       <c r="B66" t="n">
-        <v>90688</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>övernattning</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>376748</v>
+        <v>376843</v>
       </c>
       <c r="R66" t="n">
-        <v>6928890</v>
+        <v>6928942</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7391,32 +7066,27 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120463009</v>
+        <v>120461318</v>
       </c>
       <c r="B67" t="n">
-        <v>78590</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79328</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -7427,17 +7097,17 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>376424</v>
+        <v>376890</v>
       </c>
       <c r="R67" t="n">
-        <v>6928913</v>
+        <v>6928691</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7481,49 +7151,44 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120461918</v>
+        <v>120462799</v>
       </c>
       <c r="B68" t="n">
-        <v>74698</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79328</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6440</v>
+        <v>230405</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7533,13 +7198,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>376774</v>
+        <v>376432</v>
       </c>
       <c r="R68" t="n">
-        <v>6928741</v>
+        <v>6928842</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7583,49 +7248,44 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120462773</v>
+        <v>120462872</v>
       </c>
       <c r="B69" t="n">
-        <v>79672</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79328</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2081</v>
+        <v>230405</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7635,13 +7295,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>376533</v>
+        <v>376420</v>
       </c>
       <c r="R69" t="n">
-        <v>6928800</v>
+        <v>6928868</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7685,49 +7345,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120462344</v>
+        <v>120462971</v>
       </c>
       <c r="B70" t="n">
-        <v>90688</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79328</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5432</v>
+        <v>230405</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7737,13 +7392,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>376677</v>
+        <v>376410</v>
       </c>
       <c r="R70" t="n">
-        <v>6928749</v>
+        <v>6928948</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7787,65 +7442,60 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120463172</v>
+        <v>120463131</v>
       </c>
       <c r="B71" t="n">
-        <v>90958</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79328</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>658</v>
+        <v>230405</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>376427</v>
+        <v>376470</v>
       </c>
       <c r="R71" t="n">
-        <v>6928969</v>
+        <v>6928960</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7889,49 +7539,44 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120461553</v>
+        <v>120463161</v>
       </c>
       <c r="B72" t="n">
-        <v>79672</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79328</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2081</v>
+        <v>230405</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7941,13 +7586,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>376797</v>
+        <v>376500</v>
       </c>
       <c r="R72" t="n">
-        <v>6928714</v>
+        <v>6928936</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7991,65 +7636,60 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120462877</v>
+        <v>120463433</v>
       </c>
       <c r="B73" t="n">
-        <v>74698</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79328</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6440</v>
+        <v>230405</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Rödtjärnbäcken, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>376442</v>
+        <v>376511</v>
       </c>
       <c r="R73" t="n">
-        <v>6928809</v>
+        <v>6928908</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8093,44 +7733,39 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120462931</v>
+        <v>120463512</v>
       </c>
       <c r="B74" t="n">
-        <v>78590</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79328</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -8145,13 +7780,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>376436</v>
+        <v>376585</v>
       </c>
       <c r="R74" t="n">
-        <v>6928867</v>
+        <v>6928865</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8195,12 +7830,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>

--- a/artfynd/A 38064-2024 artfynd.xlsx
+++ b/artfynd/A 38064-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY74"/>
+  <dimension ref="A1:AZ74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120463172</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120463650</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120463914</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120461364</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120462911</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120463175</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120464218</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120464264</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120462738</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120461377</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120461382</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120461419</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120461553</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120461838</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120462773</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120463199</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120463458</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120464020</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2524,6 +2619,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120315911</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2621,6 +2721,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120459553</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2718,6 +2823,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120459601</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2815,6 +2925,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120461491</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2912,6 +3027,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120461902</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3009,6 +3129,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120461976</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3106,6 +3231,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120462219</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3203,6 +3333,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120462372</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3300,6 +3435,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120462634</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3397,6 +3537,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120462766</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3494,6 +3639,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120462783</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3591,6 +3741,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120462884</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3688,6 +3843,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120462917</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3785,6 +3945,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120462931</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3882,6 +4047,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120463009</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3979,6 +4149,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120463089</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4076,6 +4251,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120463133</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4173,6 +4353,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120463188</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4270,6 +4455,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120463768</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4367,6 +4557,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120463773</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4464,6 +4659,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120464038</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4561,6 +4761,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120464085</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4658,6 +4863,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120464111</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4755,6 +4965,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120464178</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4852,6 +5067,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120464210</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4949,6 +5169,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120464355</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5046,6 +5271,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120464383</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5143,6 +5373,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120464475</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5240,6 +5475,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120461333</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5337,6 +5577,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120461861</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5434,6 +5679,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120461918</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5531,6 +5781,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120461973</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5628,6 +5883,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120462573</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5725,6 +5985,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120462796</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5822,6 +6087,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120462877</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5919,6 +6189,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120463769</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6016,6 +6291,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120463824</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6113,6 +6393,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120464351</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6219,6 +6504,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120315928</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6316,6 +6606,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120461440</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6413,6 +6708,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120461329</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6531,6 +6831,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120315897</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6636,6 +6941,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120315903</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6741,6 +7051,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120315910</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6846,6 +7161,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120315914</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6951,6 +7271,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120315938</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7063,6 +7388,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120464397</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7160,6 +7490,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120461318</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7257,6 +7592,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120462799</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7354,6 +7694,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120462872</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7451,6 +7796,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120462971</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7548,6 +7898,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120463131</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7645,6 +8000,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120463161</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7742,6 +8102,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120463433</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7839,8 +8204,88 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120463512</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>